--- a/Data/FairCarboN_Datas_Labo3.xlsx
+++ b/Data/FairCarboN_Datas_Labo3.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478DBEA6-B77D-4E0D-8923-33BADE712A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABE77AE-B0B6-457C-A098-11AFE9C90D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Liste!$A$1:$M$378</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Liste!$A$1:$M$376</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4101" uniqueCount="1442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4085" uniqueCount="1442">
   <si>
     <t>Libellé structure</t>
   </si>
@@ -3631,9 +3631,6 @@
     <t>-2.129974</t>
   </si>
   <si>
-    <t>Estuaire de la Canche</t>
-  </si>
-  <si>
     <t>50.5395128</t>
   </si>
   <si>
@@ -4306,24 +4303,6 @@
     <t>5.85564275044604</t>
   </si>
   <si>
-    <t>Seudre</t>
-  </si>
-  <si>
-    <t>45.7090902</t>
-  </si>
-  <si>
-    <t>-1.0288487</t>
-  </si>
-  <si>
-    <t>Baie de Veys</t>
-  </si>
-  <si>
-    <t>49.3583261</t>
-  </si>
-  <si>
-    <t>-1.1165393</t>
-  </si>
-  <si>
     <t>Anse du Cul du Loup</t>
   </si>
   <si>
@@ -4454,17 +4433,54 @@
   </si>
   <si>
     <t>Gouvernance</t>
+  </si>
+  <si>
+    <t>2 boulevard Lavoisier
+49045 Angers Cedex 1</t>
+  </si>
+  <si>
+    <t>47.27541</t>
+  </si>
+  <si>
+    <t>Estuaires de la Canche et de l'Authie</t>
+  </si>
+  <si>
+    <t>-0.5515588</t>
+  </si>
+  <si>
+    <t>4 allée Adolphe Bobierre - CS 61103
+ 35011 Rennes Cedex - France</t>
+  </si>
+  <si>
+    <t>48.1148</t>
+  </si>
+  <si>
+    <t>-1.710532</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4683,10 +4699,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4694,61 +4710,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4757,37 +4773,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4796,13 +4818,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5035,7 +5060,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:O467"/>
+  <dimension ref="A1:O465"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.54296875" style="4" bestFit="1" customWidth="1"/>
@@ -5058,7 +5083,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="3" customFormat="1" ht="42" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
-        <v>1440</v>
+        <v>1433</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>488</v>
@@ -5097,10 +5122,10 @@
         <v>4</v>
       </c>
       <c r="N1" s="31" t="s">
-        <v>1401</v>
+        <v>1394</v>
       </c>
       <c r="O1" s="31" t="s">
-        <v>1411</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="93.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
@@ -5144,7 +5169,7 @@
         <v>77</v>
       </c>
       <c r="N2" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O2" s="23" t="str">
         <f>"DATA/logos/" &amp; TEXT(E2,"jjj") &amp; ".png"</f>
@@ -5192,7 +5217,7 @@
         <v>168</v>
       </c>
       <c r="N3" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O3" s="23" t="str">
         <f t="shared" ref="O3:O66" si="0">"DATA/logos/" &amp; TEXT(E3,"jjj") &amp; ".png"</f>
@@ -5240,7 +5265,7 @@
         <v>168</v>
       </c>
       <c r="N4" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O4" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5286,7 +5311,7 @@
         <v>160</v>
       </c>
       <c r="N5" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O5" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5332,7 +5357,7 @@
         <v>160</v>
       </c>
       <c r="N6" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O6" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5380,7 +5405,7 @@
         <v>110</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O7" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5428,7 +5453,7 @@
         <v>110</v>
       </c>
       <c r="N8" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O8" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5476,7 +5501,7 @@
         <v>11</v>
       </c>
       <c r="N9" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O9" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5524,7 +5549,7 @@
         <v>11</v>
       </c>
       <c r="N10" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O10" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5572,7 +5597,7 @@
         <v>210</v>
       </c>
       <c r="N11" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O11" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5620,7 +5645,7 @@
         <v>210</v>
       </c>
       <c r="N12" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O12" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5662,7 +5687,7 @@
         <v>519</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O13" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5674,7 +5699,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>1425</v>
+        <v>1418</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>405</v>
@@ -5710,7 +5735,7 @@
         <v>226</v>
       </c>
       <c r="N14" s="38" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O14" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5756,7 +5781,7 @@
         <v>18</v>
       </c>
       <c r="N15" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O15" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5802,7 +5827,7 @@
         <v>18</v>
       </c>
       <c r="N16" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O16" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5848,7 +5873,7 @@
         <v>18</v>
       </c>
       <c r="N17" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O17" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5894,7 +5919,7 @@
         <v>18</v>
       </c>
       <c r="N18" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O18" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5940,7 +5965,7 @@
         <v>18</v>
       </c>
       <c r="N19" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O19" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5984,7 +6009,7 @@
         <v>439</v>
       </c>
       <c r="N20" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O20" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6032,7 +6057,7 @@
         <v>407</v>
       </c>
       <c r="N21" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O21" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6080,7 +6105,7 @@
         <v>407</v>
       </c>
       <c r="N22" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O22" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6128,7 +6153,7 @@
         <v>407</v>
       </c>
       <c r="N23" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O23" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6176,7 +6201,7 @@
         <v>31</v>
       </c>
       <c r="N24" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O24" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6224,7 +6249,7 @@
         <v>31</v>
       </c>
       <c r="N25" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O25" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6272,7 +6297,7 @@
         <v>5.4070900000000002</v>
       </c>
       <c r="N26" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O26" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6314,7 +6339,7 @@
         <v>545</v>
       </c>
       <c r="N27" s="32" t="s">
-        <v>1403</v>
+        <v>1396</v>
       </c>
       <c r="O27" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6360,7 +6385,7 @@
         <v>231</v>
       </c>
       <c r="N28" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O28" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6406,7 +6431,7 @@
         <v>231</v>
       </c>
       <c r="N29" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O29" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6448,7 +6473,7 @@
         <v>555</v>
       </c>
       <c r="N30" s="32" t="s">
-        <v>1404</v>
+        <v>1397</v>
       </c>
       <c r="O30" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6488,7 +6513,7 @@
         <v>446</v>
       </c>
       <c r="N31" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O31" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6534,7 +6559,7 @@
         <v>128</v>
       </c>
       <c r="N32" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O32" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6580,7 +6605,7 @@
         <v>128</v>
       </c>
       <c r="N33" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O33" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6628,7 +6653,7 @@
         <v>299</v>
       </c>
       <c r="N34" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O34" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6676,7 +6701,7 @@
         <v>179</v>
       </c>
       <c r="N35" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O35" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6722,7 +6747,7 @@
         <v>133</v>
       </c>
       <c r="N36" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O36" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6768,7 +6793,7 @@
         <v>415</v>
       </c>
       <c r="N37" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O37" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6814,7 +6839,7 @@
         <v>25</v>
       </c>
       <c r="N38" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O38" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6860,14 +6885,14 @@
         <v>25</v>
       </c>
       <c r="N39" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O39" s="23" t="str">
         <f t="shared" si="0"/>
         <v>DATA/logos/CESBIO.png</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>6</v>
       </c>
@@ -6906,7 +6931,7 @@
         <v>391</v>
       </c>
       <c r="N40" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O40" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6952,7 +6977,7 @@
         <v>189</v>
       </c>
       <c r="N41" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O41" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6998,7 +7023,7 @@
         <v>189</v>
       </c>
       <c r="N42" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O42" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7044,7 +7069,7 @@
         <v>371</v>
       </c>
       <c r="N43" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O43" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7090,7 +7115,7 @@
         <v>371</v>
       </c>
       <c r="N44" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O44" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7138,7 +7163,7 @@
         <v>310</v>
       </c>
       <c r="N45" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O45" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7186,7 +7211,7 @@
         <v>419</v>
       </c>
       <c r="N46" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O46" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7234,7 +7259,7 @@
         <v>299</v>
       </c>
       <c r="N47" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O47" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7282,7 +7307,7 @@
         <v>299</v>
       </c>
       <c r="N48" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O48" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7330,7 +7355,7 @@
         <v>299</v>
       </c>
       <c r="N49" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O49" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7378,7 +7403,7 @@
         <v>299</v>
       </c>
       <c r="N50" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O50" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7426,7 +7451,7 @@
         <v>299</v>
       </c>
       <c r="N51" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O51" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7474,7 +7499,7 @@
         <v>299</v>
       </c>
       <c r="N52" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O52" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7522,7 +7547,7 @@
         <v>299</v>
       </c>
       <c r="N53" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O53" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7570,7 +7595,7 @@
         <v>606</v>
       </c>
       <c r="N54" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O54" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7616,19 +7641,19 @@
         <v>424</v>
       </c>
       <c r="N55" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O55" s="23" t="str">
         <f t="shared" si="0"/>
         <v>DATA/logos/ECODIV.png</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="111" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15" ht="111" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>405</v>
@@ -7664,7 +7689,7 @@
         <v>31</v>
       </c>
       <c r="N56" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O56" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7712,7 +7737,7 @@
         <v>31</v>
       </c>
       <c r="N57" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O57" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7760,7 +7785,7 @@
         <v>31</v>
       </c>
       <c r="N58" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O58" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7808,7 +7833,7 @@
         <v>31</v>
       </c>
       <c r="N59" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O59" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7856,7 +7881,7 @@
         <v>31</v>
       </c>
       <c r="N60" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O60" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7898,7 +7923,7 @@
         <v>617</v>
       </c>
       <c r="N61" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O61" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7946,7 +7971,7 @@
         <v>143</v>
       </c>
       <c r="N62" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O62" s="23" t="str">
         <f t="shared" si="0"/>
@@ -7994,7 +8019,7 @@
         <v>143</v>
       </c>
       <c r="N63" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O63" s="23" t="str">
         <f t="shared" si="0"/>
@@ -8042,7 +8067,7 @@
         <v>235</v>
       </c>
       <c r="N64" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O64" s="23" t="str">
         <f t="shared" si="0"/>
@@ -8090,7 +8115,7 @@
         <v>235</v>
       </c>
       <c r="N65" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O65" s="23" t="str">
         <f t="shared" si="0"/>
@@ -8136,7 +8161,7 @@
         <v>635</v>
       </c>
       <c r="N66" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O66" s="23" t="str">
         <f t="shared" si="0"/>
@@ -8182,7 +8207,7 @@
         <v>635</v>
       </c>
       <c r="N67" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O67" s="23" t="str">
         <f t="shared" ref="O67:O130" si="1">"DATA/logos/" &amp; TEXT(E67,"jjj") &amp; ".png"</f>
@@ -8228,7 +8253,7 @@
         <v>635</v>
       </c>
       <c r="N68" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O68" s="23" t="str">
         <f t="shared" si="1"/>
@@ -8276,7 +8301,7 @@
         <v>404</v>
       </c>
       <c r="N69" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O69" s="23" t="str">
         <f t="shared" si="1"/>
@@ -8324,7 +8349,7 @@
         <v>404</v>
       </c>
       <c r="N70" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O70" s="23" t="str">
         <f t="shared" si="1"/>
@@ -8372,7 +8397,7 @@
         <v>237</v>
       </c>
       <c r="N71" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O71" s="23" t="str">
         <f t="shared" si="1"/>
@@ -8420,7 +8445,7 @@
         <v>237</v>
       </c>
       <c r="N72" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O72" s="23" t="str">
         <f t="shared" si="1"/>
@@ -8468,14 +8493,14 @@
         <v>237</v>
       </c>
       <c r="N73" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O73" s="23" t="str">
         <f t="shared" si="1"/>
         <v>DATA/logos/FARE.png</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:15" ht="87" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>6</v>
       </c>
@@ -8516,7 +8541,7 @@
         <v>395</v>
       </c>
       <c r="N74" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O74" s="23" t="str">
         <f t="shared" si="1"/>
@@ -8562,7 +8587,7 @@
         <v>360</v>
       </c>
       <c r="N75" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O75" s="23" t="str">
         <f t="shared" si="1"/>
@@ -8608,7 +8633,7 @@
         <v>191</v>
       </c>
       <c r="N76" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O76" s="23" t="str">
         <f t="shared" si="1"/>
@@ -8629,7 +8654,7 @@
         <v>654</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>1420</v>
+        <v>1413</v>
       </c>
       <c r="F77" s="13"/>
       <c r="G77" s="13" t="s">
@@ -8652,7 +8677,7 @@
         <v>349</v>
       </c>
       <c r="N77" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O77" s="23" t="str">
         <f t="shared" si="1"/>
@@ -8673,7 +8698,7 @@
         <v>195</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>1419</v>
+        <v>1412</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>658</v>
@@ -8700,7 +8725,7 @@
         <v>346</v>
       </c>
       <c r="N78" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O78" s="23" t="str">
         <f t="shared" si="1"/>
@@ -8721,7 +8746,7 @@
         <v>195</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>1419</v>
+        <v>1412</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>658</v>
@@ -8748,7 +8773,7 @@
         <v>346</v>
       </c>
       <c r="N79" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O79" s="23" t="str">
         <f t="shared" si="1"/>
@@ -8794,7 +8819,7 @@
         <v>200</v>
       </c>
       <c r="N80" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O80" s="23" t="str">
         <f t="shared" si="1"/>
@@ -8840,7 +8865,7 @@
         <v>200</v>
       </c>
       <c r="N81" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O81" s="23" t="str">
         <f t="shared" si="1"/>
@@ -8886,7 +8911,7 @@
         <v>200</v>
       </c>
       <c r="N82" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O82" s="23" t="str">
         <f t="shared" si="1"/>
@@ -8934,7 +8959,7 @@
         <v>216</v>
       </c>
       <c r="N83" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O83" s="23" t="str">
         <f t="shared" si="1"/>
@@ -8982,7 +9007,7 @@
         <v>342</v>
       </c>
       <c r="N84" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O84" s="23" t="str">
         <f t="shared" si="1"/>
@@ -9030,7 +9055,7 @@
         <v>241</v>
       </c>
       <c r="N85" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O85" s="23" t="str">
         <f t="shared" si="1"/>
@@ -9078,7 +9103,7 @@
         <v>365</v>
       </c>
       <c r="N86" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O86" s="23" t="str">
         <f t="shared" si="1"/>
@@ -9126,7 +9151,7 @@
         <v>365</v>
       </c>
       <c r="N87" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O87" s="23" t="str">
         <f t="shared" si="1"/>
@@ -9174,7 +9199,7 @@
         <v>365</v>
       </c>
       <c r="N88" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O88" s="23" t="str">
         <f t="shared" si="1"/>
@@ -9222,7 +9247,7 @@
         <v>365</v>
       </c>
       <c r="N89" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O89" s="23" t="str">
         <f t="shared" si="1"/>
@@ -9270,14 +9295,14 @@
         <v>365</v>
       </c>
       <c r="N90" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O90" s="23" t="str">
         <f t="shared" si="1"/>
         <v>DATA/logos/iEES.png</v>
       </c>
     </row>
-    <row r="91" spans="1:15" ht="134" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:15" ht="134" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>6</v>
       </c>
@@ -9318,7 +9343,7 @@
         <v>365</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O91" s="23" t="str">
         <f t="shared" si="1"/>
@@ -9366,7 +9391,7 @@
         <v>365</v>
       </c>
       <c r="N92" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O92" s="23" t="str">
         <f t="shared" si="1"/>
@@ -9414,7 +9439,7 @@
         <v>220</v>
       </c>
       <c r="N93" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O93" s="23" t="str">
         <f t="shared" si="1"/>
@@ -9462,7 +9487,7 @@
         <v>220</v>
       </c>
       <c r="N94" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O94" s="23" t="str">
         <f t="shared" si="1"/>
@@ -9510,19 +9535,19 @@
         <v>220</v>
       </c>
       <c r="N95" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O95" s="23" t="str">
         <f t="shared" si="1"/>
         <v>DATA/logos/IGE.png</v>
       </c>
     </row>
-    <row r="96" spans="1:15" ht="129.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:15" ht="129.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>405</v>
@@ -9558,7 +9583,7 @@
         <v>220</v>
       </c>
       <c r="N96" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O96" s="23" t="str">
         <f t="shared" si="1"/>
@@ -9606,7 +9631,7 @@
         <v>409</v>
       </c>
       <c r="N97" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O97" s="23" t="str">
         <f t="shared" si="1"/>
@@ -9654,7 +9679,7 @@
         <v>376</v>
       </c>
       <c r="N98" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O98" s="23" t="str">
         <f t="shared" si="1"/>
@@ -9700,7 +9725,7 @@
         <v>435</v>
       </c>
       <c r="N99" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O99" s="23" t="str">
         <f t="shared" si="1"/>
@@ -9746,19 +9771,19 @@
         <v>333</v>
       </c>
       <c r="N100" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O100" s="23" t="str">
         <f t="shared" si="1"/>
         <v>DATA/logos/Info&amp;Sols.png</v>
       </c>
     </row>
-    <row r="101" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:15" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>405</v>
@@ -9788,7 +9813,7 @@
         <v>697</v>
       </c>
       <c r="N101" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O101" s="23" t="str">
         <f t="shared" si="1"/>
@@ -9836,7 +9861,7 @@
         <v>349</v>
       </c>
       <c r="N102" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O102" s="23" t="str">
         <f t="shared" si="1"/>
@@ -9884,7 +9909,7 @@
         <v>349</v>
       </c>
       <c r="N103" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O103" s="23" t="str">
         <f t="shared" si="1"/>
@@ -9932,7 +9957,7 @@
         <v>247</v>
       </c>
       <c r="N104" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O104" s="23" t="str">
         <f t="shared" si="1"/>
@@ -9944,7 +9969,7 @@
         <v>6</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>1421</v>
+        <v>1414</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>405</v>
@@ -9980,7 +10005,7 @@
         <v>385</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>1437</v>
+        <v>1430</v>
       </c>
       <c r="O105" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10028,7 +10053,7 @@
         <v>367</v>
       </c>
       <c r="N106" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O106" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10076,7 +10101,7 @@
         <v>105</v>
       </c>
       <c r="N107" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O107" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10124,7 +10149,7 @@
         <v>105</v>
       </c>
       <c r="N108" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O108" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10172,7 +10197,7 @@
         <v>335</v>
       </c>
       <c r="N109" s="1" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O109" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10220,7 +10245,7 @@
         <v>335</v>
       </c>
       <c r="N110" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O110" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10268,7 +10293,7 @@
         <v>335</v>
       </c>
       <c r="N111" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O111" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10316,7 +10341,7 @@
         <v>365</v>
       </c>
       <c r="N112" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O112" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10364,7 +10389,7 @@
         <v>365</v>
       </c>
       <c r="N113" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O113" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10412,7 +10437,7 @@
         <v>365</v>
       </c>
       <c r="N114" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O114" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10460,7 +10485,7 @@
         <v>352</v>
       </c>
       <c r="N115" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O115" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10508,7 +10533,7 @@
         <v>354</v>
       </c>
       <c r="N116" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O116" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10556,7 +10581,7 @@
         <v>354</v>
       </c>
       <c r="N117" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O117" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10602,7 +10627,7 @@
         <v>252</v>
       </c>
       <c r="N118" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O118" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10650,7 +10675,7 @@
         <v>481</v>
       </c>
       <c r="N119" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O119" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10698,7 +10723,7 @@
         <v>481</v>
       </c>
       <c r="N120" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O120" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10744,7 +10769,7 @@
         <v>256</v>
       </c>
       <c r="N121" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O121" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10792,7 +10817,7 @@
         <v>428</v>
       </c>
       <c r="N122" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O122" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10840,7 +10865,7 @@
         <v>136</v>
       </c>
       <c r="N123" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O123" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10888,7 +10913,7 @@
         <v>136</v>
       </c>
       <c r="N124" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O124" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10936,7 +10961,7 @@
         <v>344</v>
       </c>
       <c r="N125" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O125" s="23" t="str">
         <f t="shared" si="1"/>
@@ -10984,7 +11009,7 @@
         <v>344</v>
       </c>
       <c r="N126" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O126" s="23" t="str">
         <f t="shared" si="1"/>
@@ -11032,7 +11057,7 @@
         <v>304</v>
       </c>
       <c r="N127" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O127" s="23" t="str">
         <f t="shared" si="1"/>
@@ -11080,7 +11105,7 @@
         <v>85</v>
       </c>
       <c r="N128" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O128" s="23" t="str">
         <f t="shared" si="1"/>
@@ -11128,7 +11153,7 @@
         <v>85</v>
       </c>
       <c r="N129" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O129" s="23" t="str">
         <f t="shared" si="1"/>
@@ -11172,7 +11197,7 @@
         <v>761</v>
       </c>
       <c r="N130" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O130" s="23" t="str">
         <f t="shared" si="1"/>
@@ -11220,7 +11245,7 @@
         <v>261</v>
       </c>
       <c r="N131" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O131" s="23" t="str">
         <f t="shared" ref="O131:O193" si="2">"DATA/logos/" &amp; TEXT(E131,"jjj") &amp; ".png"</f>
@@ -11268,19 +11293,19 @@
         <v>263</v>
       </c>
       <c r="N132" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O132" s="23" t="str">
         <f t="shared" si="2"/>
         <v>DATA/logos/LETG.png</v>
       </c>
     </row>
-    <row r="133" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:15" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>405</v>
@@ -11314,7 +11339,7 @@
         <v>265</v>
       </c>
       <c r="N133" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O133" s="23" t="str">
         <f t="shared" si="2"/>
@@ -11360,7 +11385,7 @@
         <v>265</v>
       </c>
       <c r="N134" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O134" s="23" t="str">
         <f t="shared" si="2"/>
@@ -11406,7 +11431,7 @@
         <v>265</v>
       </c>
       <c r="N135" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O135" s="23" t="str">
         <f t="shared" si="2"/>
@@ -11452,7 +11477,7 @@
         <v>265</v>
       </c>
       <c r="N136" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O136" s="23" t="str">
         <f t="shared" si="2"/>
@@ -11498,7 +11523,7 @@
         <v>265</v>
       </c>
       <c r="N137" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O137" s="23" t="str">
         <f t="shared" si="2"/>
@@ -11544,14 +11569,14 @@
         <v>265</v>
       </c>
       <c r="N138" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O138" s="23" t="str">
         <f t="shared" si="2"/>
         <v>DATA/logos/LG-ENS.png</v>
       </c>
     </row>
-    <row r="139" spans="1:15" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:15" ht="58" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>6</v>
       </c>
@@ -11590,7 +11615,7 @@
         <v>265</v>
       </c>
       <c r="N139" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O139" s="23" t="str">
         <f t="shared" si="2"/>
@@ -11638,7 +11663,7 @@
         <v>269</v>
       </c>
       <c r="N140" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O140" s="23" t="str">
         <f t="shared" si="2"/>
@@ -11684,7 +11709,7 @@
         <v>446</v>
       </c>
       <c r="N141" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O141" s="23" t="str">
         <f t="shared" si="2"/>
@@ -11730,7 +11755,7 @@
         <v>446</v>
       </c>
       <c r="N142" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O142" s="23" t="str">
         <f t="shared" si="2"/>
@@ -11772,7 +11797,7 @@
         <v>338</v>
       </c>
       <c r="N143" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O143" s="23" t="str">
         <f t="shared" si="2"/>
@@ -11820,7 +11845,7 @@
         <v>788</v>
       </c>
       <c r="N144" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O144" s="23" t="str">
         <f t="shared" si="2"/>
@@ -11866,7 +11891,7 @@
         <v>363</v>
       </c>
       <c r="N145" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O145" s="23" t="str">
         <f t="shared" si="2"/>
@@ -11912,7 +11937,7 @@
         <v>363</v>
       </c>
       <c r="N146" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O146" s="23" t="str">
         <f t="shared" si="2"/>
@@ -11958,7 +11983,7 @@
         <v>363</v>
       </c>
       <c r="N147" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O147" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12004,7 +12029,7 @@
         <v>363</v>
       </c>
       <c r="N148" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O148" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12050,7 +12075,7 @@
         <v>363</v>
       </c>
       <c r="N149" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O149" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12096,7 +12121,7 @@
         <v>275</v>
       </c>
       <c r="N150" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O150" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12140,7 +12165,7 @@
         <v>94</v>
       </c>
       <c r="N151" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O151" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12188,7 +12213,7 @@
         <v>387</v>
       </c>
       <c r="N152" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O152" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12236,7 +12261,7 @@
         <v>387</v>
       </c>
       <c r="N153" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O153" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12284,7 +12309,7 @@
         <v>810</v>
       </c>
       <c r="N154" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O154" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12330,7 +12355,7 @@
         <v>389</v>
       </c>
       <c r="N155" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O155" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12366,17 +12391,17 @@
         <v>45</v>
       </c>
       <c r="J156" s="5"/>
-      <c r="K156" s="8" t="s">
-        <v>98</v>
+      <c r="K156" s="40" t="s">
+        <v>1435</v>
       </c>
       <c r="L156" s="8" t="s">
-        <v>388</v>
+        <v>1436</v>
       </c>
       <c r="M156" s="8" t="s">
-        <v>389</v>
+        <v>1438</v>
       </c>
       <c r="N156" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O156" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12422,7 +12447,7 @@
         <v>389</v>
       </c>
       <c r="N157" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O157" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12468,7 +12493,7 @@
         <v>205</v>
       </c>
       <c r="N158" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O158" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12514,7 +12539,7 @@
         <v>205</v>
       </c>
       <c r="N159" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O159" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12560,7 +12585,7 @@
         <v>205</v>
       </c>
       <c r="N160" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O160" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12606,7 +12631,7 @@
         <v>205</v>
       </c>
       <c r="N161" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O161" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12654,7 +12679,7 @@
         <v>102</v>
       </c>
       <c r="N162" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O162" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12702,7 +12727,7 @@
         <v>357</v>
       </c>
       <c r="N163" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O163" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12744,7 +12769,7 @@
         <v>829</v>
       </c>
       <c r="N164" s="1" t="s">
-        <v>1405</v>
+        <v>1398</v>
       </c>
       <c r="O164" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12792,7 +12817,7 @@
         <v>365</v>
       </c>
       <c r="N165" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O165" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12840,7 +12865,7 @@
         <v>365</v>
       </c>
       <c r="N166" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O166" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12888,7 +12913,7 @@
         <v>365</v>
       </c>
       <c r="N167" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O167" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12936,7 +12961,7 @@
         <v>365</v>
       </c>
       <c r="N168" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O168" s="23" t="str">
         <f t="shared" si="2"/>
@@ -12984,14 +13009,14 @@
         <v>283</v>
       </c>
       <c r="N169" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O169" s="23" t="str">
         <f t="shared" si="2"/>
         <v>DATA/logos/OPAALE.png</v>
       </c>
     </row>
-    <row r="170" spans="1:15" ht="77.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:15" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>6</v>
       </c>
@@ -13030,7 +13055,7 @@
         <v>391</v>
       </c>
       <c r="N170" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O170" s="23" t="str">
         <f t="shared" si="2"/>
@@ -13076,7 +13101,7 @@
         <v>391</v>
       </c>
       <c r="N171" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O171" s="23" t="str">
         <f t="shared" si="2"/>
@@ -13124,14 +13149,14 @@
         <v>293</v>
       </c>
       <c r="N172" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O172" s="23" t="str">
         <f t="shared" si="2"/>
         <v>DATA/logos/PSAE.png</v>
       </c>
     </row>
-    <row r="173" spans="1:15" ht="319" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:15" ht="319" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>6</v>
       </c>
@@ -13172,14 +13197,14 @@
         <v>293</v>
       </c>
       <c r="N173" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O173" s="23" t="str">
         <f t="shared" si="2"/>
         <v>DATA/logos/PSAE.png</v>
       </c>
     </row>
-    <row r="174" spans="1:15" ht="62" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:15" ht="62" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>6</v>
       </c>
@@ -13216,7 +13241,7 @@
         <v>847</v>
       </c>
       <c r="N174" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O174" s="23" t="str">
         <f t="shared" si="2"/>
@@ -13264,7 +13289,7 @@
         <v>380</v>
       </c>
       <c r="N175" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O175" s="23" t="str">
         <f t="shared" si="2"/>
@@ -13310,7 +13335,7 @@
         <v>59</v>
       </c>
       <c r="N176" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O176" s="23" t="str">
         <f t="shared" si="2"/>
@@ -13356,7 +13381,7 @@
         <v>59</v>
       </c>
       <c r="N177" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O177" s="23" t="str">
         <f t="shared" si="2"/>
@@ -13400,7 +13425,7 @@
         <v>858</v>
       </c>
       <c r="N178" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O178" s="23" t="str">
         <f t="shared" si="2"/>
@@ -13446,7 +13471,7 @@
         <v>373</v>
       </c>
       <c r="N179" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O179" s="23" t="str">
         <f t="shared" si="2"/>
@@ -13492,7 +13517,7 @@
         <v>373</v>
       </c>
       <c r="N180" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O180" s="23" t="str">
         <f t="shared" si="2"/>
@@ -13504,7 +13529,7 @@
         <v>6</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>1422</v>
+        <v>1415</v>
       </c>
       <c r="C181" s="5" t="s">
         <v>405</v>
@@ -13531,16 +13556,16 @@
         <v>500</v>
       </c>
       <c r="K181" s="36" t="s">
-        <v>1432</v>
+        <v>1425</v>
       </c>
       <c r="L181" s="35" t="s">
-        <v>1435</v>
+        <v>1428</v>
       </c>
       <c r="M181" s="37" t="s">
-        <v>1434</v>
+        <v>1427</v>
       </c>
       <c r="N181" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O181" s="23" t="str">
         <f t="shared" si="2"/>
@@ -13552,7 +13577,7 @@
         <v>6</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>1433</v>
+        <v>1426</v>
       </c>
       <c r="C182" s="5" t="s">
         <v>405</v>
@@ -13579,16 +13604,16 @@
         <v>500</v>
       </c>
       <c r="K182" s="36" t="s">
-        <v>1432</v>
+        <v>1425</v>
       </c>
       <c r="L182" s="35" t="s">
-        <v>1431</v>
+        <v>1424</v>
       </c>
       <c r="M182" s="34" t="s">
-        <v>1430</v>
+        <v>1423</v>
       </c>
       <c r="N182" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O182" s="23" t="str">
         <f t="shared" si="2"/>
@@ -13600,7 +13625,7 @@
         <v>6</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>1424</v>
+        <v>1417</v>
       </c>
       <c r="C183" s="5" t="s">
         <v>405</v>
@@ -13627,16 +13652,16 @@
         <v>500</v>
       </c>
       <c r="K183" s="36" t="s">
-        <v>1432</v>
+        <v>1425</v>
       </c>
       <c r="L183" s="35" t="s">
-        <v>1431</v>
+        <v>1424</v>
       </c>
       <c r="M183" s="34" t="s">
-        <v>1430</v>
+        <v>1423</v>
       </c>
       <c r="N183" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O183" s="23" t="str">
         <f t="shared" si="2"/>
@@ -13684,7 +13709,7 @@
         <v>18</v>
       </c>
       <c r="N184" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O184" s="23" t="str">
         <f t="shared" si="2"/>
@@ -13732,7 +13757,7 @@
         <v>18</v>
       </c>
       <c r="N185" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O185" s="23" t="str">
         <f t="shared" si="2"/>
@@ -13780,7 +13805,7 @@
         <v>18</v>
       </c>
       <c r="N186" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O186" s="23" t="str">
         <f t="shared" si="2"/>
@@ -13826,14 +13851,14 @@
         <v>399</v>
       </c>
       <c r="N187" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O187" s="23" t="str">
         <f t="shared" si="2"/>
         <v>DATA/logos/SMART-LERECO.png</v>
       </c>
     </row>
-    <row r="188" spans="1:15" s="2" customFormat="1" ht="62" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:15" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
         <v>6</v>
       </c>
@@ -13862,17 +13887,17 @@
         <v>871</v>
       </c>
       <c r="J188" s="5"/>
-      <c r="K188" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="L188" s="8" t="s">
-        <v>398</v>
-      </c>
-      <c r="M188" s="8" t="s">
-        <v>399</v>
+      <c r="K188" s="41" t="s">
+        <v>1439</v>
+      </c>
+      <c r="L188" s="41" t="s">
+        <v>1440</v>
+      </c>
+      <c r="M188" s="42" t="s">
+        <v>1441</v>
       </c>
       <c r="N188" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O188" s="23" t="str">
         <f t="shared" si="2"/>
@@ -13916,7 +13941,7 @@
         <v>876</v>
       </c>
       <c r="N189" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O189" s="23" t="str">
         <f t="shared" si="2"/>
@@ -13964,14 +13989,14 @@
         <v>286</v>
       </c>
       <c r="N190" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O190" s="23" t="str">
         <f t="shared" si="2"/>
         <v>DATA/logos/TBI.png</v>
       </c>
     </row>
-    <row r="191" spans="1:15" s="2" customFormat="1" ht="108.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:15" s="2" customFormat="1" ht="108.5" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>6</v>
       </c>
@@ -14012,7 +14037,7 @@
         <v>401</v>
       </c>
       <c r="N191" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O191" s="23" t="str">
         <f t="shared" si="2"/>
@@ -14054,7 +14079,7 @@
         <v>893</v>
       </c>
       <c r="N192" s="1" t="s">
-        <v>1406</v>
+        <v>1399</v>
       </c>
       <c r="O192" s="23" t="str">
         <f t="shared" si="2"/>
@@ -14100,7 +14125,7 @@
         <v>340</v>
       </c>
       <c r="N193" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O193" s="23" t="str">
         <f t="shared" si="2"/>
@@ -14146,7 +14171,7 @@
         <v>382</v>
       </c>
       <c r="N194" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O194" s="23" t="str">
         <f t="shared" ref="O194:O257" si="3">"DATA/logos/" &amp; TEXT(E194,"jjj") &amp; ".png"</f>
@@ -14192,7 +14217,7 @@
         <v>382</v>
       </c>
       <c r="N195" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O195" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14232,7 +14257,7 @@
         <v>903</v>
       </c>
       <c r="N196" s="1" t="s">
-        <v>1407</v>
+        <v>1400</v>
       </c>
       <c r="O196" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14274,7 +14299,7 @@
         <v>624</v>
       </c>
       <c r="N197" s="1" t="s">
-        <v>1403</v>
+        <v>1396</v>
       </c>
       <c r="O197" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14320,7 +14345,7 @@
         <v>910</v>
       </c>
       <c r="N198" s="1" t="s">
-        <v>1408</v>
+        <v>1401</v>
       </c>
       <c r="O198" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14360,7 +14385,7 @@
         <v>915</v>
       </c>
       <c r="N199" s="1" t="s">
-        <v>1409</v>
+        <v>1402</v>
       </c>
       <c r="O199" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14408,7 +14433,7 @@
         <v>910</v>
       </c>
       <c r="N200" s="1" t="s">
-        <v>1408</v>
+        <v>1401</v>
       </c>
       <c r="O200" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14446,7 +14471,7 @@
         <v>923</v>
       </c>
       <c r="N201" s="1" t="s">
-        <v>1410</v>
+        <v>1403</v>
       </c>
       <c r="O201" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14482,7 +14507,7 @@
         <v>927</v>
       </c>
       <c r="N202" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O202" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14518,7 +14543,7 @@
         <v>930</v>
       </c>
       <c r="N203" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O203" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14554,7 +14579,7 @@
         <v>933</v>
       </c>
       <c r="N204" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O204" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14590,7 +14615,7 @@
         <v>936</v>
       </c>
       <c r="N205" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O205" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14626,7 +14651,7 @@
         <v>939</v>
       </c>
       <c r="N206" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O206" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14662,7 +14687,7 @@
         <v>942</v>
       </c>
       <c r="N207" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O207" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14698,7 +14723,7 @@
         <v>945</v>
       </c>
       <c r="N208" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O208" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14734,7 +14759,7 @@
         <v>948</v>
       </c>
       <c r="N209" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O209" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14770,7 +14795,7 @@
         <v>951</v>
       </c>
       <c r="N210" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O210" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14806,7 +14831,7 @@
         <v>954</v>
       </c>
       <c r="N211" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O211" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14842,7 +14867,7 @@
         <v>957</v>
       </c>
       <c r="N212" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O212" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14878,7 +14903,7 @@
         <v>960</v>
       </c>
       <c r="N213" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O213" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14914,7 +14939,7 @@
         <v>963</v>
       </c>
       <c r="N214" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O214" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14950,7 +14975,7 @@
         <v>966</v>
       </c>
       <c r="N215" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O215" s="23" t="str">
         <f t="shared" si="3"/>
@@ -14986,7 +15011,7 @@
         <v>969</v>
       </c>
       <c r="N216" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O216" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15022,7 +15047,7 @@
         <v>972</v>
       </c>
       <c r="N217" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O217" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15058,7 +15083,7 @@
         <v>975</v>
       </c>
       <c r="N218" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O218" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15094,7 +15119,7 @@
         <v>978</v>
       </c>
       <c r="N219" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O219" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15130,7 +15155,7 @@
         <v>981</v>
       </c>
       <c r="N220" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O220" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15166,7 +15191,7 @@
         <v>984</v>
       </c>
       <c r="N221" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O221" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15202,7 +15227,7 @@
         <v>987</v>
       </c>
       <c r="N222" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O222" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15238,7 +15263,7 @@
         <v>990</v>
       </c>
       <c r="N223" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O223" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15274,7 +15299,7 @@
         <v>993</v>
       </c>
       <c r="N224" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O224" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15310,7 +15335,7 @@
         <v>996</v>
       </c>
       <c r="N225" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O225" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15346,7 +15371,7 @@
         <v>999</v>
       </c>
       <c r="N226" s="1" t="s">
-        <v>1412</v>
+        <v>1405</v>
       </c>
       <c r="O226" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15382,7 +15407,7 @@
         <v>1002</v>
       </c>
       <c r="N227" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O227" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15418,7 +15443,7 @@
         <v>1005</v>
       </c>
       <c r="N228" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O228" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15454,7 +15479,7 @@
         <v>1008</v>
       </c>
       <c r="N229" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O229" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15490,7 +15515,7 @@
         <v>1011</v>
       </c>
       <c r="N230" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O230" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15526,7 +15551,7 @@
         <v>1014</v>
       </c>
       <c r="N231" s="1" t="s">
-        <v>1409</v>
+        <v>1402</v>
       </c>
       <c r="O231" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15562,7 +15587,7 @@
         <v>1017</v>
       </c>
       <c r="N232" s="1" t="s">
-        <v>1407</v>
+        <v>1400</v>
       </c>
       <c r="O232" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15598,7 +15623,7 @@
         <v>1020</v>
       </c>
       <c r="N233" s="1" t="s">
-        <v>1407</v>
+        <v>1400</v>
       </c>
       <c r="O233" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15634,7 +15659,7 @@
         <v>1023</v>
       </c>
       <c r="N234" s="1" t="s">
-        <v>1410</v>
+        <v>1403</v>
       </c>
       <c r="O234" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15670,7 +15695,7 @@
         <v>978</v>
       </c>
       <c r="N235" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O235" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15706,7 +15731,7 @@
         <v>981</v>
       </c>
       <c r="N236" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O236" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15742,7 +15767,7 @@
         <v>993</v>
       </c>
       <c r="N237" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O237" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15778,7 +15803,7 @@
         <v>996</v>
       </c>
       <c r="N238" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O238" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15814,7 +15839,7 @@
         <v>927</v>
       </c>
       <c r="N239" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O239" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15850,7 +15875,7 @@
         <v>930</v>
       </c>
       <c r="N240" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O240" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15886,7 +15911,7 @@
         <v>933</v>
       </c>
       <c r="N241" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O241" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15922,7 +15947,7 @@
         <v>936</v>
       </c>
       <c r="N242" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O242" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15958,7 +15983,7 @@
         <v>939</v>
       </c>
       <c r="N243" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O243" s="23" t="str">
         <f t="shared" si="3"/>
@@ -15994,7 +16019,7 @@
         <v>960</v>
       </c>
       <c r="N244" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O244" s="23" t="str">
         <f t="shared" si="3"/>
@@ -16030,7 +16055,7 @@
         <v>966</v>
       </c>
       <c r="N245" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O245" s="23" t="str">
         <f t="shared" si="3"/>
@@ -16066,7 +16091,7 @@
         <v>1002</v>
       </c>
       <c r="N246" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O246" s="23" t="str">
         <f t="shared" si="3"/>
@@ -16102,7 +16127,7 @@
         <v>1026</v>
       </c>
       <c r="N247" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O247" s="23" t="str">
         <f t="shared" si="3"/>
@@ -16138,7 +16163,7 @@
         <v>1005</v>
       </c>
       <c r="N248" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O248" s="23" t="str">
         <f t="shared" si="3"/>
@@ -16174,7 +16199,7 @@
         <v>1029</v>
       </c>
       <c r="N249" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O249" s="23" t="str">
         <f t="shared" si="3"/>
@@ -16210,7 +16235,7 @@
         <v>1032</v>
       </c>
       <c r="N250" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O250" s="23" t="str">
         <f t="shared" si="3"/>
@@ -16246,7 +16271,7 @@
         <v>1035</v>
       </c>
       <c r="N251" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O251" s="23" t="str">
         <f t="shared" si="3"/>
@@ -16282,7 +16307,7 @@
         <v>1038</v>
       </c>
       <c r="N252" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O252" s="23" t="str">
         <f t="shared" si="3"/>
@@ -16318,7 +16343,7 @@
         <v>1041</v>
       </c>
       <c r="N253" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O253" s="23" t="str">
         <f t="shared" si="3"/>
@@ -16330,7 +16355,7 @@
         <v>6</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>1422</v>
+        <v>1415</v>
       </c>
       <c r="C254" s="5" t="s">
         <v>925</v>
@@ -16354,7 +16379,7 @@
         <v>1044</v>
       </c>
       <c r="N254" s="1" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O254" s="23" t="str">
         <f t="shared" si="3"/>
@@ -16366,7 +16391,7 @@
         <v>6</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>1422</v>
+        <v>1415</v>
       </c>
       <c r="C255" s="5" t="s">
         <v>925</v>
@@ -16390,7 +16415,7 @@
         <v>1047</v>
       </c>
       <c r="N255" s="1" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O255" s="23" t="str">
         <f t="shared" si="3"/>
@@ -16402,7 +16427,7 @@
         <v>6</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>1422</v>
+        <v>1415</v>
       </c>
       <c r="C256" s="5" t="s">
         <v>925</v>
@@ -16426,7 +16451,7 @@
         <v>1050</v>
       </c>
       <c r="N256" s="1" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O256" s="23" t="str">
         <f t="shared" si="3"/>
@@ -16462,7 +16487,7 @@
         <v>1053</v>
       </c>
       <c r="N257" s="1" t="s">
-        <v>1416</v>
+        <v>1409</v>
       </c>
       <c r="O257" s="23" t="str">
         <f t="shared" si="3"/>
@@ -16498,7 +16523,7 @@
         <v>1056</v>
       </c>
       <c r="N258" s="1" t="s">
-        <v>1412</v>
+        <v>1405</v>
       </c>
       <c r="O258" s="23" t="str">
         <f t="shared" ref="O258:O318" si="4">"DATA/logos/" &amp; TEXT(E258,"jjj") &amp; ".png"</f>
@@ -16534,7 +16559,7 @@
         <v>1059</v>
       </c>
       <c r="N259" s="1" t="s">
-        <v>1414</v>
+        <v>1407</v>
       </c>
       <c r="O259" s="23" t="str">
         <f t="shared" si="4"/>
@@ -16546,7 +16571,7 @@
         <v>6</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>1423</v>
+        <v>1416</v>
       </c>
       <c r="C260" s="5" t="s">
         <v>925</v>
@@ -16570,7 +16595,7 @@
         <v>1062</v>
       </c>
       <c r="N260" s="1" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O260" s="23" t="str">
         <f t="shared" si="4"/>
@@ -16606,7 +16631,7 @@
         <v>1065</v>
       </c>
       <c r="N261" s="1" t="s">
-        <v>1413</v>
+        <v>1406</v>
       </c>
       <c r="O261" s="23" t="str">
         <f t="shared" si="4"/>
@@ -16642,7 +16667,7 @@
         <v>1068</v>
       </c>
       <c r="N262" s="1" t="s">
-        <v>1436</v>
+        <v>1429</v>
       </c>
       <c r="O262" s="23" t="str">
         <f t="shared" si="4"/>
@@ -16678,7 +16703,7 @@
         <v>1071</v>
       </c>
       <c r="N263" s="1" t="s">
-        <v>1415</v>
+        <v>1408</v>
       </c>
       <c r="O263" s="23" t="str">
         <f t="shared" si="4"/>
@@ -16714,7 +16739,7 @@
         <v>1074</v>
       </c>
       <c r="N264" s="1" t="s">
-        <v>1408</v>
+        <v>1401</v>
       </c>
       <c r="O264" s="23" t="str">
         <f t="shared" si="4"/>
@@ -16750,7 +16775,7 @@
         <v>1077</v>
       </c>
       <c r="N265" s="1" t="s">
-        <v>1417</v>
+        <v>1410</v>
       </c>
       <c r="O265" s="23" t="str">
         <f t="shared" si="4"/>
@@ -16786,7 +16811,7 @@
         <v>1080</v>
       </c>
       <c r="N266" s="1" t="s">
-        <v>1417</v>
+        <v>1410</v>
       </c>
       <c r="O266" s="23" t="str">
         <f t="shared" si="4"/>
@@ -16807,7 +16832,7 @@
         <v>1081</v>
       </c>
       <c r="E267" s="25" t="s">
-        <v>1439</v>
+        <v>1432</v>
       </c>
       <c r="F267" s="1"/>
       <c r="G267" s="1"/>
@@ -16822,7 +16847,7 @@
         <v>1083</v>
       </c>
       <c r="N267" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O267" s="23" t="str">
         <f t="shared" si="4"/>
@@ -16858,7 +16883,7 @@
         <v>1086</v>
       </c>
       <c r="N268" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O268" s="23" t="str">
         <f t="shared" si="4"/>
@@ -16879,7 +16904,7 @@
         <v>1087</v>
       </c>
       <c r="E269" s="25" t="s">
-        <v>1438</v>
+        <v>1431</v>
       </c>
       <c r="F269" s="1"/>
       <c r="G269" s="1"/>
@@ -16894,7 +16919,7 @@
         <v>1089</v>
       </c>
       <c r="N269" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O269" s="23" t="str">
         <f t="shared" si="4"/>
@@ -16930,7 +16955,7 @@
         <v>1092</v>
       </c>
       <c r="N270" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O270" s="23" t="str">
         <f t="shared" si="4"/>
@@ -16942,7 +16967,7 @@
         <v>6</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>1424</v>
+        <v>1417</v>
       </c>
       <c r="C271" s="5" t="s">
         <v>925</v>
@@ -16966,7 +16991,7 @@
         <v>1095</v>
       </c>
       <c r="N271" s="1" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O271" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17002,7 +17027,7 @@
         <v>1098</v>
       </c>
       <c r="N272" s="1" t="s">
-        <v>1408</v>
+        <v>1401</v>
       </c>
       <c r="O272" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17014,7 +17039,7 @@
         <v>6</v>
       </c>
       <c r="B273" s="33" t="s">
-        <v>1425</v>
+        <v>1418</v>
       </c>
       <c r="C273" s="5" t="s">
         <v>925</v>
@@ -17038,7 +17063,7 @@
         <v>1101</v>
       </c>
       <c r="N273" s="1" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O273" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17074,7 +17099,7 @@
         <v>1104</v>
       </c>
       <c r="N274" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O274" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17110,7 +17135,7 @@
         <v>999</v>
       </c>
       <c r="N275" s="1" t="s">
-        <v>1412</v>
+        <v>1405</v>
       </c>
       <c r="O275" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17146,7 +17171,7 @@
         <v>987</v>
       </c>
       <c r="N276" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O276" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17182,7 +17207,7 @@
         <v>984</v>
       </c>
       <c r="N277" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O277" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17218,7 +17243,7 @@
         <v>990</v>
       </c>
       <c r="N278" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O278" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17254,7 +17279,7 @@
         <v>1107</v>
       </c>
       <c r="N279" s="1" t="s">
-        <v>1428</v>
+        <v>1421</v>
       </c>
       <c r="O279" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17290,7 +17315,7 @@
         <v>1110</v>
       </c>
       <c r="N280" s="1" t="s">
-        <v>1429</v>
+        <v>1422</v>
       </c>
       <c r="O280" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17326,7 +17351,7 @@
         <v>1113</v>
       </c>
       <c r="N281" s="1" t="s">
-        <v>1406</v>
+        <v>1399</v>
       </c>
       <c r="O281" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17338,7 +17363,7 @@
         <v>6</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>1426</v>
+        <v>1419</v>
       </c>
       <c r="C282" s="5" t="s">
         <v>925</v>
@@ -17362,7 +17387,7 @@
         <v>1116</v>
       </c>
       <c r="N282" s="1" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O282" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17374,7 +17399,7 @@
         <v>6</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>1426</v>
+        <v>1419</v>
       </c>
       <c r="C283" s="5" t="s">
         <v>925</v>
@@ -17398,7 +17423,7 @@
         <v>1119</v>
       </c>
       <c r="N283" s="1" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O283" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17434,7 +17459,7 @@
         <v>1122</v>
       </c>
       <c r="N284" s="1" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O284" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17446,7 +17471,7 @@
         <v>6</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>1427</v>
+        <v>1420</v>
       </c>
       <c r="C285" s="5" t="s">
         <v>925</v>
@@ -17470,7 +17495,7 @@
         <v>-52.289486400000001</v>
       </c>
       <c r="N285" s="1" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O285" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17482,7 +17507,7 @@
         <v>6</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>1427</v>
+        <v>1420</v>
       </c>
       <c r="C286" s="5" t="s">
         <v>925</v>
@@ -17506,7 +17531,7 @@
         <v>1127</v>
       </c>
       <c r="N286" s="1" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O286" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17542,7 +17567,7 @@
         <v>1130</v>
       </c>
       <c r="N287" s="1" t="s">
-        <v>1412</v>
+        <v>1405</v>
       </c>
       <c r="O287" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17578,7 +17603,7 @@
         <v>1133</v>
       </c>
       <c r="N288" s="1" t="s">
-        <v>1412</v>
+        <v>1405</v>
       </c>
       <c r="O288" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17614,7 +17639,7 @@
         <v>1136</v>
       </c>
       <c r="N289" s="1" t="s">
-        <v>1412</v>
+        <v>1405</v>
       </c>
       <c r="O289" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17650,7 +17675,7 @@
         <v>1139</v>
       </c>
       <c r="N290" s="1" t="s">
-        <v>1409</v>
+        <v>1402</v>
       </c>
       <c r="O290" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17662,7 +17687,7 @@
         <v>6</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>1421</v>
+        <v>1414</v>
       </c>
       <c r="C291" s="5" t="s">
         <v>925</v>
@@ -17686,7 +17711,7 @@
         <v>1142</v>
       </c>
       <c r="N291" s="1" t="s">
-        <v>1437</v>
+        <v>1430</v>
       </c>
       <c r="O291" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17698,7 +17723,7 @@
         <v>6</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>1421</v>
+        <v>1414</v>
       </c>
       <c r="C292" s="5" t="s">
         <v>925</v>
@@ -17722,7 +17747,7 @@
         <v>1145</v>
       </c>
       <c r="N292" s="1" t="s">
-        <v>1437</v>
+        <v>1430</v>
       </c>
       <c r="O292" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17758,7 +17783,7 @@
         <v>1148</v>
       </c>
       <c r="N293" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O293" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17794,7 +17819,7 @@
         <v>1151</v>
       </c>
       <c r="N294" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O294" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17830,7 +17855,7 @@
         <v>1154</v>
       </c>
       <c r="N295" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O295" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17866,7 +17891,7 @@
         <v>1157</v>
       </c>
       <c r="N296" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O296" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17902,7 +17927,7 @@
         <v>1160</v>
       </c>
       <c r="N297" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O297" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17938,7 +17963,7 @@
         <v>1163</v>
       </c>
       <c r="N298" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O298" s="23" t="str">
         <f t="shared" si="4"/>
@@ -17974,14 +17999,14 @@
         <v>1166</v>
       </c>
       <c r="N299" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O299" s="23" t="str">
         <f t="shared" si="4"/>
         <v>DATA/logos/Baie de Bourgneuf.png</v>
       </c>
     </row>
-    <row r="300" spans="1:15" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:15" s="2" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" s="1" t="s">
         <v>6</v>
       </c>
@@ -17992,10 +18017,10 @@
         <v>925</v>
       </c>
       <c r="D300" s="25" t="s">
-        <v>1167</v>
+        <v>1437</v>
       </c>
       <c r="E300" s="25" t="s">
-        <v>1167</v>
+        <v>1437</v>
       </c>
       <c r="F300" s="1"/>
       <c r="G300" s="1"/>
@@ -18004,17 +18029,17 @@
       <c r="J300" s="1"/>
       <c r="K300" s="1"/>
       <c r="L300" s="25" t="s">
+        <v>1167</v>
+      </c>
+      <c r="M300" s="25" t="s">
         <v>1168</v>
       </c>
-      <c r="M300" s="25" t="s">
-        <v>1169</v>
-      </c>
       <c r="N300" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O300" s="23" t="str">
         <f t="shared" si="4"/>
-        <v>DATA/logos/Estuaire de la Canche.png</v>
+        <v>DATA/logos/Estuaires de la Canche et de l'Authie.png</v>
       </c>
     </row>
     <row r="301" spans="1:15" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -18028,10 +18053,10 @@
         <v>925</v>
       </c>
       <c r="D301" s="25" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="E301" s="25" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="F301" s="1"/>
       <c r="G301" s="1"/>
@@ -18040,13 +18065,13 @@
       <c r="J301" s="1"/>
       <c r="K301" s="1"/>
       <c r="L301" s="25" t="s">
+        <v>1170</v>
+      </c>
+      <c r="M301" s="25" t="s">
         <v>1171</v>
       </c>
-      <c r="M301" s="25" t="s">
-        <v>1172</v>
-      </c>
       <c r="N301" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O301" s="23" t="str">
         <f t="shared" si="4"/>
@@ -18064,10 +18089,10 @@
         <v>925</v>
       </c>
       <c r="D302" s="25" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="E302" s="25" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="F302" s="1"/>
       <c r="G302" s="1"/>
@@ -18076,13 +18101,13 @@
       <c r="J302" s="1"/>
       <c r="K302" s="1"/>
       <c r="L302" s="25" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M302" s="25" t="s">
         <v>1174</v>
       </c>
-      <c r="M302" s="25" t="s">
-        <v>1175</v>
-      </c>
       <c r="N302" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O302" s="23" t="str">
         <f t="shared" si="4"/>
@@ -18100,10 +18125,10 @@
         <v>925</v>
       </c>
       <c r="D303" s="25" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="E303" s="25" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="F303" s="1"/>
       <c r="G303" s="1"/>
@@ -18112,13 +18137,13 @@
       <c r="J303" s="1"/>
       <c r="K303" s="1"/>
       <c r="L303" s="25" t="s">
+        <v>1176</v>
+      </c>
+      <c r="M303" s="25" t="s">
         <v>1177</v>
       </c>
-      <c r="M303" s="25" t="s">
-        <v>1178</v>
-      </c>
       <c r="N303" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O303" s="23" t="str">
         <f t="shared" si="4"/>
@@ -18136,10 +18161,10 @@
         <v>925</v>
       </c>
       <c r="D304" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="E304" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="F304" s="1"/>
       <c r="G304" s="1"/>
@@ -18148,13 +18173,13 @@
       <c r="J304" s="1"/>
       <c r="K304" s="1"/>
       <c r="L304" s="25" t="s">
+        <v>1179</v>
+      </c>
+      <c r="M304" s="25" t="s">
         <v>1180</v>
       </c>
-      <c r="M304" s="25" t="s">
-        <v>1181</v>
-      </c>
       <c r="N304" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O304" s="23" t="str">
         <f t="shared" si="4"/>
@@ -18172,10 +18197,10 @@
         <v>925</v>
       </c>
       <c r="D305" s="25" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="E305" s="25" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="F305" s="1"/>
       <c r="G305" s="1"/>
@@ -18184,13 +18209,13 @@
       <c r="J305" s="1"/>
       <c r="K305" s="1"/>
       <c r="L305" s="25" t="s">
+        <v>1182</v>
+      </c>
+      <c r="M305" s="25" t="s">
         <v>1183</v>
       </c>
-      <c r="M305" s="25" t="s">
-        <v>1184</v>
-      </c>
       <c r="N305" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O305" s="23" t="str">
         <f t="shared" si="4"/>
@@ -18208,10 +18233,10 @@
         <v>925</v>
       </c>
       <c r="D306" s="25" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="E306" s="25" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="F306" s="1"/>
       <c r="G306" s="1"/>
@@ -18220,13 +18245,13 @@
       <c r="J306" s="1"/>
       <c r="K306" s="1"/>
       <c r="L306" s="25" t="s">
+        <v>1185</v>
+      </c>
+      <c r="M306" s="25" t="s">
         <v>1186</v>
       </c>
-      <c r="M306" s="25" t="s">
-        <v>1187</v>
-      </c>
       <c r="N306" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O306" s="23" t="str">
         <f t="shared" si="4"/>
@@ -18244,10 +18269,10 @@
         <v>925</v>
       </c>
       <c r="D307" s="25" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="E307" s="25" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="F307" s="1"/>
       <c r="G307" s="1"/>
@@ -18256,13 +18281,13 @@
       <c r="J307" s="1"/>
       <c r="K307" s="1"/>
       <c r="L307" s="25" t="s">
+        <v>1188</v>
+      </c>
+      <c r="M307" s="25" t="s">
         <v>1189</v>
       </c>
-      <c r="M307" s="25" t="s">
-        <v>1190</v>
-      </c>
       <c r="N307" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O307" s="23" t="str">
         <f t="shared" si="4"/>
@@ -18280,10 +18305,10 @@
         <v>925</v>
       </c>
       <c r="D308" s="25" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E308" s="25" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="F308" s="1"/>
       <c r="G308" s="1"/>
@@ -18292,13 +18317,13 @@
       <c r="J308" s="1"/>
       <c r="K308" s="1"/>
       <c r="L308" s="25" t="s">
+        <v>1191</v>
+      </c>
+      <c r="M308" s="25" t="s">
         <v>1192</v>
       </c>
-      <c r="M308" s="25" t="s">
-        <v>1193</v>
-      </c>
       <c r="N308" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O308" s="23" t="str">
         <f t="shared" si="4"/>
@@ -18316,10 +18341,10 @@
         <v>925</v>
       </c>
       <c r="D309" s="25" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="E309" s="25" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="F309" s="1"/>
       <c r="G309" s="1"/>
@@ -18328,13 +18353,13 @@
       <c r="J309" s="1"/>
       <c r="K309" s="1"/>
       <c r="L309" s="25" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M309" s="25" t="s">
         <v>1195</v>
       </c>
-      <c r="M309" s="25" t="s">
-        <v>1196</v>
-      </c>
       <c r="N309" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O309" s="23" t="str">
         <f t="shared" si="4"/>
@@ -18352,10 +18377,10 @@
         <v>925</v>
       </c>
       <c r="D310" s="25" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E310" s="25" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="F310" s="1"/>
       <c r="G310" s="1"/>
@@ -18364,13 +18389,13 @@
       <c r="J310" s="1"/>
       <c r="K310" s="1"/>
       <c r="L310" s="25" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M310" s="25" t="s">
         <v>1198</v>
       </c>
-      <c r="M310" s="25" t="s">
-        <v>1199</v>
-      </c>
       <c r="N310" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O310" s="23" t="str">
         <f t="shared" si="4"/>
@@ -18388,10 +18413,10 @@
         <v>925</v>
       </c>
       <c r="D311" s="25" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="E311" s="25" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="F311" s="1"/>
       <c r="G311" s="1"/>
@@ -18400,13 +18425,13 @@
       <c r="J311" s="1"/>
       <c r="K311" s="1"/>
       <c r="L311" s="25" t="s">
+        <v>1200</v>
+      </c>
+      <c r="M311" s="25" t="s">
         <v>1201</v>
       </c>
-      <c r="M311" s="25" t="s">
-        <v>1202</v>
-      </c>
       <c r="N311" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O311" s="23" t="str">
         <f t="shared" si="4"/>
@@ -18424,10 +18449,10 @@
         <v>925</v>
       </c>
       <c r="D312" s="25" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="E312" s="25" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="F312" s="1"/>
       <c r="G312" s="1"/>
@@ -18436,13 +18461,13 @@
       <c r="J312" s="1"/>
       <c r="K312" s="1"/>
       <c r="L312" s="27" t="s">
+        <v>1203</v>
+      </c>
+      <c r="M312" s="27" t="s">
         <v>1204</v>
       </c>
-      <c r="M312" s="27" t="s">
-        <v>1205</v>
-      </c>
       <c r="N312" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O312" s="23" t="str">
         <f t="shared" si="4"/>
@@ -18460,10 +18485,10 @@
         <v>925</v>
       </c>
       <c r="D313" s="27" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="E313" s="27" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F313" s="1"/>
       <c r="G313" s="1"/>
@@ -18472,13 +18497,13 @@
       <c r="J313" s="1"/>
       <c r="K313" s="1"/>
       <c r="L313" s="27" t="s">
+        <v>1206</v>
+      </c>
+      <c r="M313" s="27" t="s">
         <v>1207</v>
       </c>
-      <c r="M313" s="27" t="s">
-        <v>1208</v>
-      </c>
       <c r="N313" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O313" s="23" t="str">
         <f t="shared" si="4"/>
@@ -18496,10 +18521,10 @@
         <v>925</v>
       </c>
       <c r="D314" s="27" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="E314" s="27" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F314" s="1"/>
       <c r="G314" s="1"/>
@@ -18508,13 +18533,13 @@
       <c r="J314" s="1"/>
       <c r="K314" s="1"/>
       <c r="L314" s="27" t="s">
+        <v>1209</v>
+      </c>
+      <c r="M314" s="27" t="s">
         <v>1210</v>
       </c>
-      <c r="M314" s="27" t="s">
-        <v>1211</v>
-      </c>
       <c r="N314" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O314" s="23" t="str">
         <f t="shared" si="4"/>
@@ -18532,10 +18557,10 @@
         <v>925</v>
       </c>
       <c r="D315" s="27" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="E315" s="27" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F315" s="1"/>
       <c r="G315" s="1"/>
@@ -18544,13 +18569,13 @@
       <c r="J315" s="1"/>
       <c r="K315" s="1"/>
       <c r="L315" s="27" t="s">
+        <v>1212</v>
+      </c>
+      <c r="M315" s="27" t="s">
         <v>1213</v>
       </c>
-      <c r="M315" s="27" t="s">
-        <v>1214</v>
-      </c>
       <c r="N315" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O315" s="23" t="str">
         <f t="shared" si="4"/>
@@ -18568,10 +18593,10 @@
         <v>925</v>
       </c>
       <c r="D316" s="27" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="E316" s="27" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="F316" s="1"/>
       <c r="G316" s="1"/>
@@ -18580,13 +18605,13 @@
       <c r="J316" s="1"/>
       <c r="K316" s="1"/>
       <c r="L316" s="27" t="s">
+        <v>1215</v>
+      </c>
+      <c r="M316" s="27" t="s">
         <v>1216</v>
       </c>
-      <c r="M316" s="27" t="s">
-        <v>1217</v>
-      </c>
       <c r="N316" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O316" s="23" t="str">
         <f t="shared" si="4"/>
@@ -18604,10 +18629,10 @@
         <v>925</v>
       </c>
       <c r="D317" s="27" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="E317" s="27" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F317" s="1"/>
       <c r="G317" s="1"/>
@@ -18616,13 +18641,13 @@
       <c r="J317" s="1"/>
       <c r="K317" s="1"/>
       <c r="L317" s="27" t="s">
+        <v>1218</v>
+      </c>
+      <c r="M317" s="27" t="s">
         <v>1219</v>
       </c>
-      <c r="M317" s="27" t="s">
-        <v>1220</v>
-      </c>
       <c r="N317" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O317" s="23" t="str">
         <f t="shared" si="4"/>
@@ -18640,10 +18665,10 @@
         <v>925</v>
       </c>
       <c r="D318" s="27" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E318" s="27" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="F318" s="1"/>
       <c r="G318" s="1"/>
@@ -18652,13 +18677,13 @@
       <c r="J318" s="1"/>
       <c r="K318" s="1"/>
       <c r="L318" s="27" t="s">
+        <v>1221</v>
+      </c>
+      <c r="M318" s="27" t="s">
         <v>1222</v>
       </c>
-      <c r="M318" s="27" t="s">
-        <v>1223</v>
-      </c>
       <c r="N318" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O318" s="23" t="str">
         <f t="shared" si="4"/>
@@ -18676,10 +18701,10 @@
         <v>925</v>
       </c>
       <c r="D319" s="27" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E319" s="27" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="F319" s="1"/>
       <c r="G319" s="1"/>
@@ -18688,16 +18713,16 @@
       <c r="J319" s="1"/>
       <c r="K319" s="1"/>
       <c r="L319" s="27" t="s">
+        <v>1224</v>
+      </c>
+      <c r="M319" s="27" t="s">
         <v>1225</v>
       </c>
-      <c r="M319" s="27" t="s">
-        <v>1226</v>
-      </c>
       <c r="N319" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O319" s="23" t="str">
-        <f t="shared" ref="O319:O377" si="5">"DATA/logos/" &amp; TEXT(E319,"jjj") &amp; ".png"</f>
+        <f t="shared" ref="O319:O375" si="5">"DATA/logos/" &amp; TEXT(E319,"jjj") &amp; ".png"</f>
         <v>DATA/logos/Lac des Corbeaux.png</v>
       </c>
     </row>
@@ -18712,10 +18737,10 @@
         <v>925</v>
       </c>
       <c r="D320" s="29" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="E320" s="29" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="F320" s="1"/>
       <c r="G320" s="1"/>
@@ -18724,13 +18749,13 @@
       <c r="J320" s="1"/>
       <c r="K320" s="1"/>
       <c r="L320" s="27" t="s">
+        <v>1227</v>
+      </c>
+      <c r="M320" s="27" t="s">
         <v>1228</v>
       </c>
-      <c r="M320" s="27" t="s">
-        <v>1229</v>
-      </c>
       <c r="N320" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O320" s="23" t="str">
         <f t="shared" si="5"/>
@@ -18748,10 +18773,10 @@
         <v>925</v>
       </c>
       <c r="D321" s="27" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="E321" s="27" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="F321" s="1"/>
       <c r="G321" s="1"/>
@@ -18760,13 +18785,13 @@
       <c r="J321" s="1"/>
       <c r="K321" s="1"/>
       <c r="L321" s="27" t="s">
+        <v>1230</v>
+      </c>
+      <c r="M321" s="28" t="s">
         <v>1231</v>
       </c>
-      <c r="M321" s="28" t="s">
-        <v>1232</v>
-      </c>
       <c r="N321" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O321" s="23" t="str">
         <f t="shared" si="5"/>
@@ -18784,10 +18809,10 @@
         <v>925</v>
       </c>
       <c r="D322" s="27" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="E322" s="27" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="F322" s="1"/>
       <c r="G322" s="1"/>
@@ -18796,13 +18821,13 @@
       <c r="J322" s="1"/>
       <c r="K322" s="1"/>
       <c r="L322" s="27" t="s">
+        <v>1233</v>
+      </c>
+      <c r="M322" s="28" t="s">
         <v>1234</v>
       </c>
-      <c r="M322" s="28" t="s">
-        <v>1235</v>
-      </c>
       <c r="N322" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O322" s="23" t="str">
         <f t="shared" si="5"/>
@@ -18820,10 +18845,10 @@
         <v>925</v>
       </c>
       <c r="D323" s="27" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="E323" s="27" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="F323" s="1"/>
       <c r="G323" s="1"/>
@@ -18832,13 +18857,13 @@
       <c r="J323" s="1"/>
       <c r="K323" s="1"/>
       <c r="L323" s="27" t="s">
+        <v>1236</v>
+      </c>
+      <c r="M323" s="27" t="s">
         <v>1237</v>
       </c>
-      <c r="M323" s="27" t="s">
-        <v>1238</v>
-      </c>
       <c r="N323" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O323" s="23" t="str">
         <f t="shared" si="5"/>
@@ -18856,10 +18881,10 @@
         <v>925</v>
       </c>
       <c r="D324" s="27" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="E324" s="27" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F324" s="1"/>
       <c r="G324" s="1"/>
@@ -18868,13 +18893,13 @@
       <c r="J324" s="1"/>
       <c r="K324" s="1"/>
       <c r="L324" s="27" t="s">
+        <v>1239</v>
+      </c>
+      <c r="M324" s="27" t="s">
         <v>1240</v>
       </c>
-      <c r="M324" s="27" t="s">
-        <v>1241</v>
-      </c>
       <c r="N324" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O324" s="23" t="str">
         <f t="shared" si="5"/>
@@ -18892,10 +18917,10 @@
         <v>925</v>
       </c>
       <c r="D325" s="27" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="E325" s="27" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F325" s="1"/>
       <c r="G325" s="1"/>
@@ -18904,13 +18929,13 @@
       <c r="J325" s="1"/>
       <c r="K325" s="1"/>
       <c r="L325" s="27" t="s">
+        <v>1242</v>
+      </c>
+      <c r="M325" s="27" t="s">
         <v>1243</v>
       </c>
-      <c r="M325" s="27" t="s">
-        <v>1244</v>
-      </c>
       <c r="N325" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O325" s="23" t="str">
         <f t="shared" si="5"/>
@@ -18928,10 +18953,10 @@
         <v>925</v>
       </c>
       <c r="D326" s="27" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="E326" s="27" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="F326" s="1"/>
       <c r="G326" s="1"/>
@@ -18940,13 +18965,13 @@
       <c r="J326" s="1"/>
       <c r="K326" s="1"/>
       <c r="L326" s="27" t="s">
+        <v>1245</v>
+      </c>
+      <c r="M326" s="27" t="s">
         <v>1246</v>
       </c>
-      <c r="M326" s="27" t="s">
-        <v>1247</v>
-      </c>
       <c r="N326" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O326" s="23" t="str">
         <f t="shared" si="5"/>
@@ -18964,10 +18989,10 @@
         <v>925</v>
       </c>
       <c r="D327" s="27" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E327" s="27" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="F327" s="1"/>
       <c r="G327" s="1"/>
@@ -18976,13 +19001,13 @@
       <c r="J327" s="1"/>
       <c r="K327" s="1"/>
       <c r="L327" s="27" t="s">
+        <v>1248</v>
+      </c>
+      <c r="M327" s="27" t="s">
         <v>1249</v>
       </c>
-      <c r="M327" s="27" t="s">
-        <v>1250</v>
-      </c>
       <c r="N327" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O327" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19000,10 +19025,10 @@
         <v>925</v>
       </c>
       <c r="D328" s="27" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="E328" s="27" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="F328" s="1"/>
       <c r="G328" s="1"/>
@@ -19012,13 +19037,13 @@
       <c r="J328" s="1"/>
       <c r="K328" s="1"/>
       <c r="L328" s="27" t="s">
+        <v>1251</v>
+      </c>
+      <c r="M328" s="27" t="s">
         <v>1252</v>
       </c>
-      <c r="M328" s="27" t="s">
-        <v>1253</v>
-      </c>
       <c r="N328" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O328" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19036,10 +19061,10 @@
         <v>925</v>
       </c>
       <c r="D329" s="27" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="E329" s="27" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="F329" s="1"/>
       <c r="G329" s="1"/>
@@ -19048,13 +19073,13 @@
       <c r="J329" s="1"/>
       <c r="K329" s="1"/>
       <c r="L329" s="25" t="s">
+        <v>1254</v>
+      </c>
+      <c r="M329" s="25" t="s">
         <v>1255</v>
       </c>
-      <c r="M329" s="25" t="s">
-        <v>1256</v>
-      </c>
       <c r="N329" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O329" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19072,10 +19097,10 @@
         <v>925</v>
       </c>
       <c r="D330" s="25" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="E330" s="25" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="F330" s="1"/>
       <c r="G330" s="1"/>
@@ -19084,13 +19109,13 @@
       <c r="J330" s="1"/>
       <c r="K330" s="1"/>
       <c r="L330" s="25" t="s">
+        <v>1257</v>
+      </c>
+      <c r="M330" s="25" t="s">
         <v>1258</v>
       </c>
-      <c r="M330" s="25" t="s">
-        <v>1259</v>
-      </c>
       <c r="N330" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O330" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19108,10 +19133,10 @@
         <v>925</v>
       </c>
       <c r="D331" s="25" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E331" s="25" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="F331" s="1"/>
       <c r="G331" s="1"/>
@@ -19120,13 +19145,13 @@
       <c r="J331" s="1"/>
       <c r="K331" s="1"/>
       <c r="L331" s="25" t="s">
+        <v>1260</v>
+      </c>
+      <c r="M331" s="25" t="s">
         <v>1261</v>
       </c>
-      <c r="M331" s="25" t="s">
-        <v>1262</v>
-      </c>
       <c r="N331" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O331" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19144,10 +19169,10 @@
         <v>925</v>
       </c>
       <c r="D332" s="25" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="E332" s="25" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="F332" s="1"/>
       <c r="G332" s="1"/>
@@ -19159,10 +19184,10 @@
         <v>45.9914196</v>
       </c>
       <c r="M332" s="27" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="N332" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O332" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19180,10 +19205,10 @@
         <v>925</v>
       </c>
       <c r="D333" s="25" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="E333" s="25" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="F333" s="1"/>
       <c r="G333" s="1"/>
@@ -19195,10 +19220,10 @@
         <v>44.233585499999997</v>
       </c>
       <c r="M333" s="27" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="N333" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O333" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19216,10 +19241,10 @@
         <v>925</v>
       </c>
       <c r="D334" s="25" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="E334" s="25" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="F334" s="1"/>
       <c r="G334" s="1"/>
@@ -19228,13 +19253,13 @@
       <c r="J334" s="1"/>
       <c r="K334" s="1"/>
       <c r="L334" s="27" t="s">
+        <v>1267</v>
+      </c>
+      <c r="M334" s="27" t="s">
         <v>1268</v>
       </c>
-      <c r="M334" s="27" t="s">
-        <v>1269</v>
-      </c>
       <c r="N334" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O334" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19252,10 +19277,10 @@
         <v>925</v>
       </c>
       <c r="D335" s="25" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="E335" s="25" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="F335" s="1"/>
       <c r="G335" s="1"/>
@@ -19264,13 +19289,13 @@
       <c r="J335" s="1"/>
       <c r="K335" s="1"/>
       <c r="L335" s="27" t="s">
+        <v>1270</v>
+      </c>
+      <c r="M335" s="27" t="s">
         <v>1271</v>
       </c>
-      <c r="M335" s="27" t="s">
-        <v>1272</v>
-      </c>
       <c r="N335" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O335" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19288,10 +19313,10 @@
         <v>925</v>
       </c>
       <c r="D336" s="25" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="E336" s="25" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="F336" s="1"/>
       <c r="G336" s="1"/>
@@ -19300,13 +19325,13 @@
       <c r="J336" s="1"/>
       <c r="K336" s="1"/>
       <c r="L336" s="27" t="s">
+        <v>1273</v>
+      </c>
+      <c r="M336" s="27" t="s">
         <v>1274</v>
       </c>
-      <c r="M336" s="27" t="s">
-        <v>1275</v>
-      </c>
       <c r="N336" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O336" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19324,10 +19349,10 @@
         <v>925</v>
       </c>
       <c r="D337" s="27" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="E337" s="27" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="F337" s="1"/>
       <c r="G337" s="1"/>
@@ -19336,13 +19361,13 @@
       <c r="J337" s="1"/>
       <c r="K337" s="1"/>
       <c r="L337" s="27" t="s">
+        <v>1276</v>
+      </c>
+      <c r="M337" s="27" t="s">
         <v>1277</v>
       </c>
-      <c r="M337" s="27" t="s">
-        <v>1278</v>
-      </c>
       <c r="N337" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O337" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19360,10 +19385,10 @@
         <v>925</v>
       </c>
       <c r="D338" s="27" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="E338" s="27" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="F338" s="1"/>
       <c r="G338" s="1"/>
@@ -19372,13 +19397,13 @@
       <c r="J338" s="1"/>
       <c r="K338" s="1"/>
       <c r="L338" s="27" t="s">
+        <v>1279</v>
+      </c>
+      <c r="M338" s="27" t="s">
         <v>1280</v>
       </c>
-      <c r="M338" s="27" t="s">
-        <v>1281</v>
-      </c>
       <c r="N338" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O338" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19396,10 +19421,10 @@
         <v>925</v>
       </c>
       <c r="D339" s="27" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="E339" s="27" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="F339" s="1"/>
       <c r="G339" s="1"/>
@@ -19408,13 +19433,13 @@
       <c r="J339" s="1"/>
       <c r="K339" s="1"/>
       <c r="L339" s="27" t="s">
+        <v>1282</v>
+      </c>
+      <c r="M339" s="27" t="s">
         <v>1283</v>
       </c>
-      <c r="M339" s="27" t="s">
-        <v>1284</v>
-      </c>
       <c r="N339" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O339" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19432,10 +19457,10 @@
         <v>925</v>
       </c>
       <c r="D340" s="27" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="E340" s="27" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="F340" s="1"/>
       <c r="G340" s="1"/>
@@ -19444,13 +19469,13 @@
       <c r="J340" s="1"/>
       <c r="K340" s="1"/>
       <c r="L340" s="27" t="s">
+        <v>1285</v>
+      </c>
+      <c r="M340" s="27" t="s">
         <v>1286</v>
       </c>
-      <c r="M340" s="27" t="s">
-        <v>1287</v>
-      </c>
       <c r="N340" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O340" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19468,10 +19493,10 @@
         <v>925</v>
       </c>
       <c r="D341" s="27" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="E341" s="27" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="F341" s="1"/>
       <c r="G341" s="1"/>
@@ -19480,13 +19505,13 @@
       <c r="J341" s="1"/>
       <c r="K341" s="1"/>
       <c r="L341" s="27" t="s">
+        <v>1288</v>
+      </c>
+      <c r="M341" s="27" t="s">
         <v>1289</v>
       </c>
-      <c r="M341" s="27" t="s">
-        <v>1290</v>
-      </c>
       <c r="N341" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O341" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19504,10 +19529,10 @@
         <v>925</v>
       </c>
       <c r="D342" s="27" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="E342" s="27" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="F342" s="1"/>
       <c r="G342" s="1"/>
@@ -19516,13 +19541,13 @@
       <c r="J342" s="1"/>
       <c r="K342" s="1"/>
       <c r="L342" s="27" t="s">
+        <v>1291</v>
+      </c>
+      <c r="M342" s="27" t="s">
         <v>1292</v>
       </c>
-      <c r="M342" s="27" t="s">
-        <v>1293</v>
-      </c>
       <c r="N342" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O342" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19540,10 +19565,10 @@
         <v>925</v>
       </c>
       <c r="D343" s="27" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="E343" s="27" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="F343" s="1"/>
       <c r="G343" s="1"/>
@@ -19552,13 +19577,13 @@
       <c r="J343" s="1"/>
       <c r="K343" s="1"/>
       <c r="L343" s="27" t="s">
+        <v>1294</v>
+      </c>
+      <c r="M343" s="27" t="s">
         <v>1295</v>
       </c>
-      <c r="M343" s="27" t="s">
-        <v>1296</v>
-      </c>
       <c r="N343" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O343" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19576,10 +19601,10 @@
         <v>925</v>
       </c>
       <c r="D344" s="27" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="E344" s="27" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="F344" s="1"/>
       <c r="G344" s="1"/>
@@ -19588,13 +19613,13 @@
       <c r="J344" s="1"/>
       <c r="K344" s="1"/>
       <c r="L344" s="27" t="s">
+        <v>1297</v>
+      </c>
+      <c r="M344" s="27" t="s">
         <v>1298</v>
       </c>
-      <c r="M344" s="27" t="s">
-        <v>1299</v>
-      </c>
       <c r="N344" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O344" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19612,10 +19637,10 @@
         <v>925</v>
       </c>
       <c r="D345" s="27" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="E345" s="27" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="F345" s="1"/>
       <c r="G345" s="1"/>
@@ -19624,13 +19649,13 @@
       <c r="J345" s="1"/>
       <c r="K345" s="1"/>
       <c r="L345" s="27" t="s">
+        <v>1300</v>
+      </c>
+      <c r="M345" s="27" t="s">
         <v>1301</v>
       </c>
-      <c r="M345" s="27" t="s">
-        <v>1302</v>
-      </c>
       <c r="N345" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O345" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19648,10 +19673,10 @@
         <v>925</v>
       </c>
       <c r="D346" s="27" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="E346" s="27" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="F346" s="1"/>
       <c r="G346" s="1"/>
@@ -19660,13 +19685,13 @@
       <c r="J346" s="1"/>
       <c r="K346" s="1"/>
       <c r="L346" s="27" t="s">
+        <v>1303</v>
+      </c>
+      <c r="M346" s="27" t="s">
         <v>1304</v>
       </c>
-      <c r="M346" s="27" t="s">
-        <v>1305</v>
-      </c>
       <c r="N346" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O346" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19684,10 +19709,10 @@
         <v>925</v>
       </c>
       <c r="D347" s="27" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E347" s="27" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="F347" s="1"/>
       <c r="G347" s="1"/>
@@ -19696,13 +19721,13 @@
       <c r="J347" s="1"/>
       <c r="K347" s="1"/>
       <c r="L347" s="27" t="s">
+        <v>1306</v>
+      </c>
+      <c r="M347" s="27" t="s">
         <v>1307</v>
       </c>
-      <c r="M347" s="27" t="s">
-        <v>1308</v>
-      </c>
       <c r="N347" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O347" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19720,10 +19745,10 @@
         <v>925</v>
       </c>
       <c r="D348" s="27" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="E348" s="27" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="F348" s="1"/>
       <c r="G348" s="1"/>
@@ -19732,13 +19757,13 @@
       <c r="J348" s="1"/>
       <c r="K348" s="1"/>
       <c r="L348" s="27" t="s">
+        <v>1309</v>
+      </c>
+      <c r="M348" s="27" t="s">
         <v>1310</v>
       </c>
-      <c r="M348" s="27" t="s">
-        <v>1311</v>
-      </c>
       <c r="N348" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O348" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19756,10 +19781,10 @@
         <v>925</v>
       </c>
       <c r="D349" s="27" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E349" s="27" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="F349" s="1"/>
       <c r="G349" s="1"/>
@@ -19768,13 +19793,13 @@
       <c r="J349" s="1"/>
       <c r="K349" s="1"/>
       <c r="L349" s="27" t="s">
+        <v>1312</v>
+      </c>
+      <c r="M349" s="27" t="s">
         <v>1313</v>
       </c>
-      <c r="M349" s="27" t="s">
-        <v>1314</v>
-      </c>
       <c r="N349" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O349" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19792,10 +19817,10 @@
         <v>925</v>
       </c>
       <c r="D350" s="27" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="E350" s="27" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="F350" s="1"/>
       <c r="G350" s="1"/>
@@ -19804,13 +19829,13 @@
       <c r="J350" s="1"/>
       <c r="K350" s="1"/>
       <c r="L350" s="27" t="s">
+        <v>1315</v>
+      </c>
+      <c r="M350" s="27" t="s">
         <v>1316</v>
       </c>
-      <c r="M350" s="27" t="s">
-        <v>1317</v>
-      </c>
       <c r="N350" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O350" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19828,10 +19853,10 @@
         <v>925</v>
       </c>
       <c r="D351" s="27" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E351" s="27" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="F351" s="1"/>
       <c r="G351" s="1"/>
@@ -19840,13 +19865,13 @@
       <c r="J351" s="1"/>
       <c r="K351" s="1"/>
       <c r="L351" s="27" t="s">
+        <v>1318</v>
+      </c>
+      <c r="M351" s="27" t="s">
         <v>1319</v>
       </c>
-      <c r="M351" s="27" t="s">
-        <v>1320</v>
-      </c>
       <c r="N351" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O351" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19864,10 +19889,10 @@
         <v>925</v>
       </c>
       <c r="D352" s="27" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E352" s="27" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="F352" s="1"/>
       <c r="G352" s="1"/>
@@ -19876,13 +19901,13 @@
       <c r="J352" s="1"/>
       <c r="K352" s="1"/>
       <c r="L352" s="27" t="s">
+        <v>1321</v>
+      </c>
+      <c r="M352" s="27" t="s">
         <v>1322</v>
       </c>
-      <c r="M352" s="27" t="s">
-        <v>1323</v>
-      </c>
       <c r="N352" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O352" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19900,10 +19925,10 @@
         <v>925</v>
       </c>
       <c r="D353" s="27" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E353" s="27" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="F353" s="1"/>
       <c r="G353" s="1"/>
@@ -19912,13 +19937,13 @@
       <c r="J353" s="1"/>
       <c r="K353" s="1"/>
       <c r="L353" s="27" t="s">
+        <v>1324</v>
+      </c>
+      <c r="M353" s="27" t="s">
         <v>1325</v>
       </c>
-      <c r="M353" s="27" t="s">
-        <v>1326</v>
-      </c>
       <c r="N353" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O353" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19936,10 +19961,10 @@
         <v>925</v>
       </c>
       <c r="D354" s="27" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="E354" s="27" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="F354" s="1"/>
       <c r="G354" s="1"/>
@@ -19948,13 +19973,13 @@
       <c r="J354" s="1"/>
       <c r="K354" s="1"/>
       <c r="L354" s="27" t="s">
+        <v>1327</v>
+      </c>
+      <c r="M354" s="27" t="s">
         <v>1328</v>
       </c>
-      <c r="M354" s="27" t="s">
-        <v>1329</v>
-      </c>
       <c r="N354" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O354" s="23" t="str">
         <f t="shared" si="5"/>
@@ -19972,10 +19997,10 @@
         <v>925</v>
       </c>
       <c r="D355" s="27" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="E355" s="27" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="F355" s="1"/>
       <c r="G355" s="1"/>
@@ -19984,13 +20009,13 @@
       <c r="J355" s="1"/>
       <c r="K355" s="1"/>
       <c r="L355" s="27" t="s">
+        <v>1330</v>
+      </c>
+      <c r="M355" s="27" t="s">
         <v>1331</v>
       </c>
-      <c r="M355" s="27" t="s">
-        <v>1332</v>
-      </c>
       <c r="N355" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O355" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20008,10 +20033,10 @@
         <v>925</v>
       </c>
       <c r="D356" s="27" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="E356" s="27" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="F356" s="1"/>
       <c r="G356" s="1"/>
@@ -20020,13 +20045,13 @@
       <c r="J356" s="1"/>
       <c r="K356" s="1"/>
       <c r="L356" s="27" t="s">
+        <v>1333</v>
+      </c>
+      <c r="M356" s="27" t="s">
         <v>1334</v>
       </c>
-      <c r="M356" s="27" t="s">
-        <v>1335</v>
-      </c>
       <c r="N356" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O356" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20044,10 +20069,10 @@
         <v>925</v>
       </c>
       <c r="D357" s="27" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="E357" s="27" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="F357" s="1"/>
       <c r="G357" s="1"/>
@@ -20056,13 +20081,13 @@
       <c r="J357" s="1"/>
       <c r="K357" s="1"/>
       <c r="L357" s="27" t="s">
+        <v>1336</v>
+      </c>
+      <c r="M357" s="27" t="s">
         <v>1337</v>
       </c>
-      <c r="M357" s="27" t="s">
-        <v>1338</v>
-      </c>
       <c r="N357" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O357" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20080,10 +20105,10 @@
         <v>925</v>
       </c>
       <c r="D358" s="27" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="E358" s="27" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="F358" s="1"/>
       <c r="G358" s="1"/>
@@ -20092,13 +20117,13 @@
       <c r="J358" s="1"/>
       <c r="K358" s="1"/>
       <c r="L358" s="27" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M358" s="27" t="s">
         <v>1340</v>
       </c>
-      <c r="M358" s="27" t="s">
-        <v>1341</v>
-      </c>
       <c r="N358" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O358" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20116,10 +20141,10 @@
         <v>925</v>
       </c>
       <c r="D359" s="27" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="E359" s="27" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="F359" s="1"/>
       <c r="G359" s="1"/>
@@ -20128,13 +20153,13 @@
       <c r="J359" s="1"/>
       <c r="K359" s="1"/>
       <c r="L359" s="27" t="s">
+        <v>1342</v>
+      </c>
+      <c r="M359" s="27" t="s">
         <v>1343</v>
       </c>
-      <c r="M359" s="27" t="s">
-        <v>1344</v>
-      </c>
       <c r="N359" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O359" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20152,10 +20177,10 @@
         <v>925</v>
       </c>
       <c r="D360" s="27" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="E360" s="27" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="F360" s="1"/>
       <c r="G360" s="1"/>
@@ -20164,13 +20189,13 @@
       <c r="J360" s="1"/>
       <c r="K360" s="1"/>
       <c r="L360" s="27" t="s">
+        <v>1345</v>
+      </c>
+      <c r="M360" s="27" t="s">
         <v>1346</v>
       </c>
-      <c r="M360" s="27" t="s">
-        <v>1347</v>
-      </c>
       <c r="N360" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O360" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20188,10 +20213,10 @@
         <v>925</v>
       </c>
       <c r="D361" s="27" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="E361" s="27" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="F361" s="1"/>
       <c r="G361" s="1"/>
@@ -20200,13 +20225,13 @@
       <c r="J361" s="1"/>
       <c r="K361" s="1"/>
       <c r="L361" s="27" t="s">
+        <v>1348</v>
+      </c>
+      <c r="M361" s="27" t="s">
         <v>1349</v>
       </c>
-      <c r="M361" s="27" t="s">
-        <v>1350</v>
-      </c>
       <c r="N361" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O361" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20224,10 +20249,10 @@
         <v>925</v>
       </c>
       <c r="D362" s="27" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="E362" s="27" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="F362" s="1"/>
       <c r="G362" s="1"/>
@@ -20236,13 +20261,13 @@
       <c r="J362" s="1"/>
       <c r="K362" s="1"/>
       <c r="L362" s="27" t="s">
+        <v>1351</v>
+      </c>
+      <c r="M362" s="27" t="s">
         <v>1352</v>
       </c>
-      <c r="M362" s="27" t="s">
-        <v>1353</v>
-      </c>
       <c r="N362" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O362" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20260,10 +20285,10 @@
         <v>925</v>
       </c>
       <c r="D363" s="27" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E363" s="27" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="F363" s="1"/>
       <c r="G363" s="1"/>
@@ -20272,13 +20297,13 @@
       <c r="J363" s="1"/>
       <c r="K363" s="1"/>
       <c r="L363" s="27" t="s">
+        <v>1354</v>
+      </c>
+      <c r="M363" s="28" t="s">
         <v>1355</v>
       </c>
-      <c r="M363" s="28" t="s">
-        <v>1356</v>
-      </c>
       <c r="N363" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O363" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20296,10 +20321,10 @@
         <v>925</v>
       </c>
       <c r="D364" s="27" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E364" s="27" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="F364" s="1"/>
       <c r="G364" s="1"/>
@@ -20308,13 +20333,13 @@
       <c r="J364" s="1"/>
       <c r="K364" s="1"/>
       <c r="L364" s="27" t="s">
+        <v>1357</v>
+      </c>
+      <c r="M364" s="27" t="s">
         <v>1358</v>
       </c>
-      <c r="M364" s="27" t="s">
-        <v>1359</v>
-      </c>
       <c r="N364" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O364" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20332,10 +20357,10 @@
         <v>925</v>
       </c>
       <c r="D365" s="27" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E365" s="27" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F365" s="1"/>
       <c r="G365" s="1"/>
@@ -20344,13 +20369,13 @@
       <c r="J365" s="1"/>
       <c r="K365" s="1"/>
       <c r="L365" s="27" t="s">
+        <v>1360</v>
+      </c>
+      <c r="M365" s="27" t="s">
         <v>1361</v>
       </c>
-      <c r="M365" s="27" t="s">
-        <v>1362</v>
-      </c>
       <c r="N365" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O365" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20368,10 +20393,10 @@
         <v>925</v>
       </c>
       <c r="D366" s="27" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="E366" s="27" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="F366" s="1"/>
       <c r="G366" s="1"/>
@@ -20380,13 +20405,13 @@
       <c r="J366" s="1"/>
       <c r="K366" s="1"/>
       <c r="L366" s="27" t="s">
+        <v>1363</v>
+      </c>
+      <c r="M366" s="27" t="s">
         <v>1364</v>
       </c>
-      <c r="M366" s="27" t="s">
-        <v>1365</v>
-      </c>
       <c r="N366" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O366" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20404,10 +20429,10 @@
         <v>925</v>
       </c>
       <c r="D367" s="27" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="E367" s="27" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="F367" s="1"/>
       <c r="G367" s="1"/>
@@ -20416,13 +20441,13 @@
       <c r="J367" s="1"/>
       <c r="K367" s="1"/>
       <c r="L367" s="27" t="s">
+        <v>1366</v>
+      </c>
+      <c r="M367" s="27" t="s">
         <v>1367</v>
       </c>
-      <c r="M367" s="27" t="s">
-        <v>1368</v>
-      </c>
       <c r="N367" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O367" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20440,10 +20465,10 @@
         <v>925</v>
       </c>
       <c r="D368" s="27" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="E368" s="27" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="F368" s="1"/>
       <c r="G368" s="1"/>
@@ -20452,13 +20477,13 @@
       <c r="J368" s="1"/>
       <c r="K368" s="1"/>
       <c r="L368" s="27" t="s">
+        <v>1369</v>
+      </c>
+      <c r="M368" s="28" t="s">
         <v>1370</v>
       </c>
-      <c r="M368" s="28" t="s">
-        <v>1371</v>
-      </c>
       <c r="N368" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O368" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20476,10 +20501,10 @@
         <v>925</v>
       </c>
       <c r="D369" s="25" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="E369" s="25" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="F369" s="1"/>
       <c r="G369" s="1"/>
@@ -20488,13 +20513,13 @@
       <c r="J369" s="1"/>
       <c r="K369" s="1"/>
       <c r="L369" s="27" t="s">
+        <v>1372</v>
+      </c>
+      <c r="M369" s="27" t="s">
         <v>1373</v>
       </c>
-      <c r="M369" s="27" t="s">
-        <v>1374</v>
-      </c>
       <c r="N369" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O369" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20512,10 +20537,10 @@
         <v>925</v>
       </c>
       <c r="D370" s="25" t="s">
-        <v>1418</v>
+        <v>1411</v>
       </c>
       <c r="E370" s="25" t="s">
-        <v>1418</v>
+        <v>1411</v>
       </c>
       <c r="F370" s="1"/>
       <c r="G370" s="1"/>
@@ -20524,13 +20549,13 @@
       <c r="J370" s="1"/>
       <c r="K370" s="1"/>
       <c r="L370" s="27" t="s">
+        <v>1374</v>
+      </c>
+      <c r="M370" s="27" t="s">
         <v>1375</v>
       </c>
-      <c r="M370" s="27" t="s">
-        <v>1376</v>
-      </c>
       <c r="N370" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O370" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20548,10 +20573,10 @@
         <v>925</v>
       </c>
       <c r="D371" s="25" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="E371" s="25" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="F371" s="1"/>
       <c r="G371" s="1"/>
@@ -20560,13 +20585,13 @@
       <c r="J371" s="1"/>
       <c r="K371" s="1"/>
       <c r="L371" s="27" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M371" s="27" t="s">
         <v>1378</v>
       </c>
-      <c r="M371" s="27" t="s">
-        <v>1379</v>
-      </c>
       <c r="N371" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O371" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20584,10 +20609,10 @@
         <v>925</v>
       </c>
       <c r="D372" s="25" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="E372" s="25" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="F372" s="1"/>
       <c r="G372" s="1"/>
@@ -20596,13 +20621,13 @@
       <c r="J372" s="1"/>
       <c r="K372" s="1"/>
       <c r="L372" s="25" t="s">
+        <v>1380</v>
+      </c>
+      <c r="M372" s="25" t="s">
         <v>1381</v>
       </c>
-      <c r="M372" s="25" t="s">
-        <v>1382</v>
-      </c>
       <c r="N372" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O372" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20620,10 +20645,10 @@
         <v>925</v>
       </c>
       <c r="D373" s="25" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="E373" s="25" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="F373" s="1"/>
       <c r="G373" s="1"/>
@@ -20632,13 +20657,13 @@
       <c r="J373" s="1"/>
       <c r="K373" s="1"/>
       <c r="L373" s="25" t="s">
+        <v>1383</v>
+      </c>
+      <c r="M373" s="25" t="s">
         <v>1384</v>
       </c>
-      <c r="M373" s="25" t="s">
-        <v>1385</v>
-      </c>
       <c r="N373" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O373" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20656,10 +20681,10 @@
         <v>925</v>
       </c>
       <c r="D374" s="22" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="E374" s="22" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F374" s="1"/>
       <c r="G374" s="1"/>
@@ -20668,13 +20693,13 @@
       <c r="J374" s="1"/>
       <c r="K374" s="1"/>
       <c r="L374" s="24" t="s">
+        <v>1386</v>
+      </c>
+      <c r="M374" s="24" t="s">
         <v>1387</v>
       </c>
-      <c r="M374" s="24" t="s">
-        <v>1388</v>
-      </c>
       <c r="N374" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O374" s="23" t="str">
         <f t="shared" si="5"/>
@@ -20692,10 +20717,10 @@
         <v>925</v>
       </c>
       <c r="D375" s="30" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E375" s="30" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="F375" s="1"/>
       <c r="G375" s="1"/>
@@ -20704,20 +20729,20 @@
       <c r="J375" s="1"/>
       <c r="K375" s="1"/>
       <c r="L375" s="24" t="s">
+        <v>1389</v>
+      </c>
+      <c r="M375" s="24" t="s">
         <v>1390</v>
       </c>
-      <c r="M375" s="24" t="s">
-        <v>1391</v>
-      </c>
       <c r="N375" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O375" s="23" t="str">
         <f t="shared" si="5"/>
         <v>DATA/logos/Greoux.png</v>
       </c>
     </row>
-    <row r="376" spans="1:15" s="2" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:15" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" s="1" t="s">
         <v>6</v>
       </c>
@@ -20728,10 +20753,10 @@
         <v>925</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="F376" s="1"/>
       <c r="G376" s="1"/>
@@ -20740,90 +20765,48 @@
       <c r="J376" s="1"/>
       <c r="K376" s="1"/>
       <c r="L376" s="1" t="s">
+        <v>1392</v>
+      </c>
+      <c r="M376" s="1" t="s">
         <v>1393</v>
       </c>
-      <c r="M376" s="1" t="s">
-        <v>1394</v>
-      </c>
       <c r="N376" s="32" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="O376" s="23" t="str">
-        <f t="shared" si="5"/>
-        <v>DATA/logos/Seudre.png</v>
-      </c>
-    </row>
-    <row r="377" spans="1:15" ht="29" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A377" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B377" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C377" s="5" t="s">
-        <v>925</v>
-      </c>
-      <c r="D377" s="1" t="s">
-        <v>1395</v>
-      </c>
-      <c r="E377" s="1" t="s">
-        <v>1395</v>
-      </c>
-      <c r="F377" s="1"/>
-      <c r="G377" s="1"/>
-      <c r="H377" s="1"/>
-      <c r="I377" s="1"/>
-      <c r="J377" s="1"/>
-      <c r="K377" s="1"/>
-      <c r="L377" s="1" t="s">
-        <v>1396</v>
-      </c>
-      <c r="M377" s="1" t="s">
-        <v>1397</v>
-      </c>
-      <c r="N377" s="32" t="s">
-        <v>1402</v>
-      </c>
-      <c r="O377" s="23" t="str">
-        <f t="shared" si="5"/>
-        <v>DATA/logos/Baie de Veys.png</v>
-      </c>
-    </row>
-    <row r="378" spans="1:15" ht="29" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A378" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B378" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C378" s="5" t="s">
-        <v>925</v>
-      </c>
-      <c r="D378" s="1" t="s">
-        <v>1398</v>
-      </c>
-      <c r="E378" s="1" t="s">
-        <v>1398</v>
-      </c>
-      <c r="F378" s="1"/>
-      <c r="G378" s="1"/>
-      <c r="H378" s="1"/>
-      <c r="I378" s="1"/>
-      <c r="J378" s="1"/>
-      <c r="K378" s="1"/>
-      <c r="L378" s="1" t="s">
-        <v>1399</v>
-      </c>
-      <c r="M378" s="1" t="s">
-        <v>1400</v>
-      </c>
-      <c r="N378" s="32" t="s">
-        <v>1402</v>
-      </c>
-      <c r="O378" s="23" t="str">
-        <f t="shared" ref="O378" si="6">"DATA/logos/" &amp; TEXT(E378,"jjj") &amp; ".png"</f>
+        <f t="shared" ref="O376" si="6">"DATA/logos/" &amp; TEXT(E376,"jjj") &amp; ".png"</f>
         <v>DATA/logos/Anse du Cul du Loup.png</v>
       </c>
+    </row>
+    <row r="377" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A377" s="19"/>
+      <c r="B377" s="12"/>
+      <c r="C377" s="12"/>
+      <c r="D377" s="19"/>
+      <c r="E377" s="12"/>
+      <c r="F377" s="19"/>
+      <c r="G377" s="19"/>
+      <c r="H377" s="19"/>
+      <c r="I377" s="19"/>
+      <c r="J377" s="19"/>
+      <c r="K377" s="19"/>
+      <c r="L377" s="19"/>
+      <c r="M377" s="19"/>
+    </row>
+    <row r="378" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A378" s="19"/>
+      <c r="B378" s="12"/>
+      <c r="C378" s="12"/>
+      <c r="D378" s="19"/>
+      <c r="E378" s="12"/>
+      <c r="F378" s="19"/>
+      <c r="G378" s="19"/>
+      <c r="H378" s="19"/>
+      <c r="I378" s="19"/>
+      <c r="J378" s="19"/>
+      <c r="K378" s="19"/>
+      <c r="L378" s="19"/>
+      <c r="M378" s="19"/>
     </row>
     <row r="379" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A379" s="19"/>
@@ -22130,45 +22113,15 @@
       <c r="L465" s="19"/>
       <c r="M465" s="19"/>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A466" s="19"/>
-      <c r="B466" s="12"/>
-      <c r="C466" s="12"/>
-      <c r="D466" s="19"/>
-      <c r="E466" s="12"/>
-      <c r="F466" s="19"/>
-      <c r="G466" s="19"/>
-      <c r="H466" s="19"/>
-      <c r="I466" s="19"/>
-      <c r="J466" s="19"/>
-      <c r="K466" s="19"/>
-      <c r="L466" s="19"/>
-      <c r="M466" s="19"/>
-    </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A467" s="19"/>
-      <c r="B467" s="12"/>
-      <c r="C467" s="12"/>
-      <c r="D467" s="19"/>
-      <c r="E467" s="12"/>
-      <c r="F467" s="19"/>
-      <c r="G467" s="19"/>
-      <c r="H467" s="19"/>
-      <c r="I467" s="19"/>
-      <c r="J467" s="19"/>
-      <c r="K467" s="19"/>
-      <c r="L467" s="19"/>
-      <c r="M467" s="19"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M378" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <autoFilter ref="A1:M376" xr:uid="{00000000-0001-0000-0100-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="PEPR"/>
+        <filter val="PREFALIM"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
